--- a/files/九龙-马头角-壹沐第2期.xlsx
+++ b/files/九龙-马头角-壹沐第2期.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7007,7 +6871,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -7977,14 +7841,14 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
-        <v>7969700</v>
+        <v>7882200</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>22901</v>
+        <v>22650</v>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
@@ -20079,3714 +19943,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:P33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>壹沐第2期 - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>415 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>65 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>281 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>69 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>Q</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 684呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 269呎 (1房)
-$816万
-$30,346/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$1,052万
-$30,063/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 348呎 (2房)
-$1,049万
-$30,144/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$1,051万
-$30,207/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 957呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>G | 270呎 (1房)
-$726万
-$26,889/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>H | 265呎 (1房)
-$723万
-$27,294/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J6" s="17" t="inlineStr">
-        <is>
-          <t>J | 349呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K6" s="16" t="inlineStr">
-        <is>
-          <t>K | 273呎 (1房)
-$751万
-$27,498/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L6" s="16" t="inlineStr">
-        <is>
-          <t>L | 273呎 (1房)
-$745万
-$27,275/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="M6" s="18" t="inlineStr"/>
-      <c r="N6" s="18" t="inlineStr"/>
-      <c r="O6" s="18" t="inlineStr"/>
-      <c r="P6" s="18" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-$1,471万
-$28,729/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 397呎 (3房)
-$1,130万
-$28,458/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$911万
-$26,030/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$913万
-$26,084/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F7" s="19" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$862万
-$24,778/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G7" s="19" t="inlineStr">
-        <is>
-          <t>F | 348呎 (2房)
-$901万
-$25,893/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H7" s="19" t="inlineStr">
-        <is>
-          <t>G | 348呎 (2房)
-$853万
-$24,517/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I7" s="19" t="inlineStr">
-        <is>
-          <t>H | 348呎 (2房)
-$810万
-$23,276/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J7" s="17" t="inlineStr">
-        <is>
-          <t>J | 464呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K7" s="17" t="inlineStr">
-        <is>
-          <t>K | 395呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L7" s="19" t="inlineStr">
-        <is>
-          <t>L | 270呎 (1房)
-$548万
-$20,300/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M7" s="19" t="inlineStr">
-        <is>
-          <t>M | 265呎 (1房)
-$546万
-$20,605/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N7" s="17" t="inlineStr">
-        <is>
-          <t>N | 349呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O7" s="19" t="inlineStr">
-        <is>
-          <t>P | 273呎 (1房)
-$567万
-$20,763/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P7" s="19" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$561万
-$20,565/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-$1,196万
-$23,368/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>B | 397呎 (3房)
-$906万
-$22,831/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$803万
-$22,929/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$804万
-$22,978/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F8" s="19" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$802万
-$23,038/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 348呎 (2房)
-$958万
-$27,537/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 348呎 (2房)
-$959万
-$27,546/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>H | 348呎 (2房)
-$961万
-$27,606/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J8" s="17" t="inlineStr">
-        <is>
-          <t>J | 464呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K8" s="17" t="inlineStr">
-        <is>
-          <t>K | 395呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L8" s="19" t="inlineStr">
-        <is>
-          <t>L | 270呎 (1房)
-$525万
-$19,430/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M8" s="19" t="inlineStr">
-        <is>
-          <t>M | 265呎 (1房)
-$552万
-$20,814/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="N8" s="17" t="inlineStr">
-        <is>
-          <t>N | 349呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O8" s="19" t="inlineStr">
-        <is>
-          <t>P | 273呎 (1房)
-$542万
-$19,840/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P8" s="19" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$536万
-$19,642/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-$1,190万
-$23,237/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>B | 397呎 (3房)
-$901万
-$22,702/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$811万
-$23,181/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$844万
-$24,119/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F9" s="19" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$797万
-$22,909/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G9" s="19" t="inlineStr">
-        <is>
-          <t>F | 348呎 (2房)
-$858万
-$24,644/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 348呎 (2房)
-$953万
-$27,391/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>H | 348呎 (2房)
-$955万
-$27,451/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J9" s="17" t="inlineStr">
-        <is>
-          <t>J | 464呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K9" s="17" t="inlineStr">
-        <is>
-          <t>K | 395呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L9" s="19" t="inlineStr">
-        <is>
-          <t>L | 270呎 (1房)
-$523万
-$19,373/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M9" s="19" t="inlineStr">
-        <is>
-          <t>M | 265呎 (1房)
-$521万
-$19,661/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N9" s="17" t="inlineStr">
-        <is>
-          <t>N | 349呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O9" s="19" t="inlineStr">
-        <is>
-          <t>P | 273呎 (1房)
-$543万
-$19,893/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P9" s="19" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$535万
-$19,586/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-$1,218万
-$23,783/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>B | 397呎 (3房)
-$946万
-$23,829/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$794万
-$22,672/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$795万
-$22,724/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F10" s="19" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$837万
-$24,045/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>F | 348呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 348呎 (2房)
-$948万
-$27,239/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>H | 348呎 (2房)
-$950万
-$27,299/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>J | 464呎 (3房)
-$1,306万
-$28,157/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K10" s="17" t="inlineStr">
-        <is>
-          <t>K | 395呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L10" s="19" t="inlineStr">
-        <is>
-          <t>L | 270呎 (1房)
-$522万
-$19,320/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M10" s="19" t="inlineStr">
-        <is>
-          <t>M | 265呎 (1房)
-$520万
-$19,606/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N10" s="17" t="inlineStr">
-        <is>
-          <t>N | 349呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O10" s="19" t="inlineStr">
-        <is>
-          <t>P | 273呎 (1房)
-$538万
-$19,724/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P10" s="19" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$533万
-$19,526/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-$1,211万
-$23,648/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>B | 397呎 (3房)
-$954万
-$24,029/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$833万
-$23,796/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$835万
-$23,850/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F11" s="19" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$788万
-$22,650/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>F | 348呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H11" s="19" t="inlineStr">
-        <is>
-          <t>G | 348呎 (2房)
-$761万
-$21,861/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I11" s="19" t="inlineStr">
-        <is>
-          <t>H | 348呎 (2房)
-$805万
-$23,128/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="inlineStr">
-        <is>
-          <t>J | 464呎 (3房)
-$1,299万
-$28,000/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K11" s="16" t="inlineStr">
-        <is>
-          <t>K | 395呎 (3房)
-$1,059万
-$26,810/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L11" s="19" t="inlineStr">
-        <is>
-          <t>L | 270呎 (1房)
-$523万
-$19,374/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M11" s="19" t="inlineStr">
-        <is>
-          <t>M | 265呎 (1房)
-$547万
-$20,638/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N11" s="17" t="inlineStr">
-        <is>
-          <t>N | 349呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O11" s="19" t="inlineStr">
-        <is>
-          <t>P | 273呎 (1房)
-$537万
-$19,668/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P11" s="19" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$534万
-$19,578/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-$1,161万
-$22,671/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 397呎 (3房)
-$1,048万
-$26,406/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$812万
-$23,207/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$828万
-$23,646/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F12" s="19" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$816万
-$23,444/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>F | 348呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H12" s="19" t="inlineStr">
-        <is>
-          <t>G | 348呎 (2房)
-$761万
-$21,861/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I12" s="19" t="inlineStr">
-        <is>
-          <t>H | 348呎 (2房)
-$813万
-$23,371/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J12" s="19" t="inlineStr">
-        <is>
-          <t>J | 464呎 (3房)
-$1,133万
-$24,417/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K12" s="16" t="inlineStr">
-        <is>
-          <t>K | 395呎 (3房)
-$1,059万
-$26,810/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L12" s="19" t="inlineStr">
-        <is>
-          <t>L | 270呎 (1房)
-$523万
-$19,374/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M12" s="19" t="inlineStr">
-        <is>
-          <t>M | 265呎 (1房)
-$518万
-$19,552/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N12" s="17" t="inlineStr">
-        <is>
-          <t>N | 349呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O12" s="16" t="inlineStr">
-        <is>
-          <t>P | 273呎 (1房)
-$674万
-$24,696/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="P12" s="19" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$601万
-$22,002/呎
-(26年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-$1,148万
-$22,412/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>B | 397呎 (3房)
-$933万
-$23,491/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$807万
-$23,070/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$805万
-$22,994/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F13" s="19" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$802万
-$23,051/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>F | 348呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H13" s="19" t="inlineStr">
-        <is>
-          <t>G | 348呎 (2房)
-$752万
-$21,613/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I13" s="19" t="inlineStr">
-        <is>
-          <t>H | 348呎 (2房)
-$804万
-$23,106/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J13" s="19" t="inlineStr">
-        <is>
-          <t>J | 464呎 (3房)
-$1,061万
-$22,872/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K13" s="16" t="inlineStr">
-        <is>
-          <t>K | 395呎 (3房)
-$1,032万
-$26,139/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L13" s="19" t="inlineStr">
-        <is>
-          <t>L | 270呎 (1房)
-$517万
-$19,157/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M13" s="19" t="inlineStr">
-        <is>
-          <t>M | 265呎 (1房)
-$544万
-$20,520/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="N13" s="17" t="inlineStr">
-        <is>
-          <t>N | 349呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O13" s="16" t="inlineStr">
-        <is>
-          <t>P | 273呎 (1房)
-$670万
-$24,549/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="P13" s="19" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$597万
-$21,870/呎
-(26年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-$1,141万
-$22,282/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>B | 397呎 (3房)
-$927万
-$23,355/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$798万
-$22,811/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$800万
-$22,860/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F14" s="19" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$797万
-$22,916/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 348呎 (2房)
-$926万
-$26,612/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H14" s="19" t="inlineStr">
-        <is>
-          <t>G | 348呎 (2房)
-$824万
-$23,677/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I14" s="19" t="inlineStr">
-        <is>
-          <t>H | 348呎 (2房)
-$799万
-$22,974/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J14" s="19" t="inlineStr">
-        <is>
-          <t>J | 464呎 (3房)
-$1,055万
-$22,742/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K14" s="16" t="inlineStr">
-        <is>
-          <t>K | 395呎 (3房)
-$1,026万
-$25,987/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L14" s="19" t="inlineStr">
-        <is>
-          <t>L | 270呎 (1房)
-$583万
-$21,583/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M14" s="19" t="inlineStr">
-        <is>
-          <t>M | 265呎 (1房)
-$580万
-$21,906/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="N14" s="17" t="inlineStr">
-        <is>
-          <t>N | 349呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O14" s="16" t="inlineStr">
-        <is>
-          <t>P | 273呎 (1房)
-$668万
-$24,480/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="P14" s="19" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$595万
-$21,808/呎
-(26年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-$1,134万
-$22,152/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>B | 397呎 (3房)
-$973万
-$24,509/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$794万
-$22,677/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E15" s="19" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$796万
-$22,729/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F15" s="19" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$797万
-$22,911/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>F | 348呎 (2房)
-$921万
-$26,460/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H15" s="19" t="inlineStr">
-        <is>
-          <t>G | 348呎 (2房)
-$819万
-$23,540/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I15" s="19" t="inlineStr">
-        <is>
-          <t>H | 348呎 (2房)
-$821万
-$23,594/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J15" s="19" t="inlineStr">
-        <is>
-          <t>J | 464呎 (3房)
-$1,107万
-$23,867/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K15" s="16" t="inlineStr">
-        <is>
-          <t>K | 395呎 (3房)
-$1,020万
-$25,835/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L15" s="19" t="inlineStr">
-        <is>
-          <t>L | 270呎 (1房)
-$581万
-$21,523/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M15" s="19" t="inlineStr">
-        <is>
-          <t>M | 265呎 (1房)
-$579万
-$21,841/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="N15" s="17" t="inlineStr">
-        <is>
-          <t>N | 349呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O15" s="16" t="inlineStr">
-        <is>
-          <t>P | 273呎 (1房)
-$666万
-$24,403/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="P15" s="19" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$594万
-$21,742/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-$1,126万
-$21,987/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>B | 397呎 (3房)
-$891万
-$22,443/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$789万
-$22,546/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$835万
-$23,853/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$797万
-$22,901/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G16" s="19" t="inlineStr">
-        <is>
-          <t>F | 348呎 (2房)
-$824万
-$23,674/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H16" s="19" t="inlineStr">
-        <is>
-          <t>G | 348呎 (2房)
-$814万
-$23,403/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>H | 348呎 (2房)
-$907万
-$26,063/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J16" s="19" t="inlineStr">
-        <is>
-          <t>J | 464呎 (3房)
-$1,043万
-$22,481/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K16" s="16" t="inlineStr">
-        <is>
-          <t>K | 395呎 (3房)
-$1,014万
-$25,684/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L16" s="19" t="inlineStr">
-        <is>
-          <t>L | 270呎 (1房)
-$580万
-$21,463/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="M16" s="19" t="inlineStr">
-        <is>
-          <t>M | 265呎 (1房)
-$609万
-$22,990/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="N16" s="17" t="inlineStr">
-        <is>
-          <t>N | 349呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O16" s="19" t="inlineStr">
-        <is>
-          <t>P | 273呎 (1房)
-$529万
-$19,381/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="P16" s="19" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$524万
-$19,184/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-$1,136万
-$22,184/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>B | 397呎 (3房)
-$860万
-$21,675/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$793万
-$22,645/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E17" s="19" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$794万
-$22,697/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F17" s="19" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$792万
-$22,751/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>F | 348呎 (2房)
-$910万
-$26,152/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H17" s="19" t="inlineStr">
-        <is>
-          <t>G | 348呎 (2房)
-$810万
-$23,266/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I17" s="19" t="inlineStr">
-        <is>
-          <t>H | 348呎 (2房)
-$812万
-$23,320/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J17" s="19" t="inlineStr">
-        <is>
-          <t>J | 464呎 (3房)
-$1,084万
-$23,352/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K17" s="19" t="inlineStr">
-        <is>
-          <t>K | 395呎 (3房)
-$845万
-$21,384/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L17" s="19" t="inlineStr">
-        <is>
-          <t>L | 270呎 (1房)
-$511万
-$18,937/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M17" s="19" t="inlineStr">
-        <is>
-          <t>M | 265呎 (1房)
-$575万
-$21,715/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="N17" s="17" t="inlineStr">
-        <is>
-          <t>N | 349呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O17" s="19" t="inlineStr">
-        <is>
-          <t>P | 273呎 (1房)
-$527万
-$19,322/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="P17" s="19" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$522万
-$19,124/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-$1,129万
-$22,052/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>B | 397呎 (3房)
-$855万
-$21,546/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$746万
-$21,327/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E18" s="19" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$790万
-$22,564/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$746万
-$21,427/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G18" s="19" t="inlineStr">
-        <is>
-          <t>F | 348呎 (2房)
-$814万
-$23,397/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H18" s="19" t="inlineStr">
-        <is>
-          <t>G | 348呎 (2房)
-$850万
-$24,416/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I18" s="19" t="inlineStr">
-        <is>
-          <t>H | 348呎 (2房)
-$807万
-$23,183/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J18" s="19" t="inlineStr">
-        <is>
-          <t>J | 464呎 (3房)
-$1,077万
-$23,214/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K18" s="19" t="inlineStr">
-        <is>
-          <t>K | 395呎 (3房)
-$882万
-$22,332/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L18" s="19" t="inlineStr">
-        <is>
-          <t>L | 270呎 (1房)
-$538万
-$19,932/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M18" s="19" t="inlineStr">
-        <is>
-          <t>M | 265呎 (1房)
-$508万
-$19,162/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N18" s="17" t="inlineStr">
-        <is>
-          <t>N | 349呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O18" s="19" t="inlineStr">
-        <is>
-          <t>P | 273呎 (1房)
-$555万
-$20,336/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P18" s="19" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$521万
-$19,068/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-$1,256万
-$24,537/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>B | 397呎 (3房)
-$850万
-$21,416/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$783万
-$22,379/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$744万
-$21,250/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$741万
-$21,300/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>F | 348呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H19" s="19" t="inlineStr">
-        <is>
-          <t>G | 348呎 (2房)
-$800万
-$22,994/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I19" s="19" t="inlineStr">
-        <is>
-          <t>H | 348呎 (2房)
-$847万
-$24,326/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>J | 464呎 (3房)
-$1,241万
-$26,741/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K19" s="19" t="inlineStr">
-        <is>
-          <t>K | 395呎 (3房)
-$872万
-$22,074/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L19" s="19" t="inlineStr">
-        <is>
-          <t>L | 270呎 (1房)
-$509万
-$18,863/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M19" s="19" t="inlineStr">
-        <is>
-          <t>M | 265呎 (1房)
-$534万
-$20,169/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N19" s="17" t="inlineStr">
-        <is>
-          <t>N | 349呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O19" s="19" t="inlineStr">
-        <is>
-          <t>P | 273呎 (1房)
-$553万
-$20,274/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P19" s="19" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$519万
-$19,009/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-$1,183万
-$23,105/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>B | 397呎 (3房)
-$845万
-$21,287/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$738万
-$21,075/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E20" s="19" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$739万
-$21,124/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$737万
-$21,173/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>F | 348呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H20" s="19" t="inlineStr">
-        <is>
-          <t>G | 348呎 (2房)
-$795万
-$22,857/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I20" s="19" t="inlineStr">
-        <is>
-          <t>H | 348呎 (2房)
-$797万
-$22,909/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>J | 464呎 (3房)
-$1,234万
-$26,584/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="K20" s="19" t="inlineStr">
-        <is>
-          <t>K | 395呎 (3房)
-$867万
-$21,942/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L20" s="19" t="inlineStr">
-        <is>
-          <t>L | 270呎 (1房)
-$536万
-$19,866/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M20" s="19" t="inlineStr">
-        <is>
-          <t>M | 265呎 (1房)
-$503万
-$18,995/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="N20" s="17" t="inlineStr">
-        <is>
-          <t>N | 349呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O20" s="19" t="inlineStr">
-        <is>
-          <t>P | 273呎 (1房)
-$521万
-$19,095/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P20" s="19" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$545万
-$19,947/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-$1,333万
-$26,035/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>B | 397呎 (3房)
-$870万
-$21,906/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$893万
-$25,526/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$895万
-$25,583/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$892万
-$25,644/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>F | 348呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H21" s="19" t="inlineStr">
-        <is>
-          <t>G | 348呎 (2房)
-$795万
-$22,857/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I21" s="19" t="inlineStr">
-        <is>
-          <t>H | 348呎 (2房)
-$797万
-$22,909/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J21" s="17" t="inlineStr">
-        <is>
-          <t>J | 464呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K21" s="19" t="inlineStr">
-        <is>
-          <t>K | 395呎 (3房)
-$876万
-$22,186/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L21" s="19" t="inlineStr">
-        <is>
-          <t>L | 270呎 (1房)
-$508万
-$18,800/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M21" s="19" t="inlineStr">
-        <is>
-          <t>M | 265呎 (1房)
-$503万
-$18,995/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="N21" s="17" t="inlineStr">
-        <is>
-          <t>N | 349呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O21" s="19" t="inlineStr">
-        <is>
-          <t>P | 273呎 (1房)
-$521万
-$19,095/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P21" s="19" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$516万
-$18,897/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-$1,251万
-$24,437/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>B | 397呎 (3房)
-$896万
-$22,575/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$794万
-$22,695/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E22" s="19" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$796万
-$22,747/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F22" s="19" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$793万
-$22,800/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>F | 348呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H22" s="19" t="inlineStr">
-        <is>
-          <t>G | 348呎 (2房)
-$786万
-$22,583/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I22" s="19" t="inlineStr">
-        <is>
-          <t>H | 348呎 (2房)
-$788万
-$22,637/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J22" s="17" t="inlineStr">
-        <is>
-          <t>J | 464呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K22" s="19" t="inlineStr">
-        <is>
-          <t>K | 395呎 (3房)
-$856万
-$21,675/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L22" s="19" t="inlineStr">
-        <is>
-          <t>L | 270呎 (1房)
-$568万
-$21,044/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M22" s="19" t="inlineStr">
-        <is>
-          <t>M | 265呎 (1房)
-$501万
-$18,917/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N22" s="17" t="inlineStr">
-        <is>
-          <t>N | 349呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O22" s="19" t="inlineStr">
-        <is>
-          <t>P | 273呎 (1房)
-$518万
-$18,979/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="P22" s="19" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$514万
-$18,814/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-$1,309万
-$25,564/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 397呎 (3房)
-$990万
-$24,929/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$877万
-$25,063/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$879万
-$25,123/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$876万
-$25,181/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>F | 348呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H23" s="19" t="inlineStr">
-        <is>
-          <t>G | 348呎 (2房)
-$794万
-$22,820/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I23" s="19" t="inlineStr">
-        <is>
-          <t>H | 348呎 (2房)
-$792万
-$22,750/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J23" s="17" t="inlineStr">
-        <is>
-          <t>J | 464呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K23" s="19" t="inlineStr">
-        <is>
-          <t>K | 395呎 (3房)
-$924万
-$23,387/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L23" s="19" t="inlineStr">
-        <is>
-          <t>L | 270呎 (1房)
-$537万
-$19,877/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M23" s="19" t="inlineStr">
-        <is>
-          <t>M | 265呎 (1房)
-$535万
-$20,170/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N23" s="17" t="inlineStr">
-        <is>
-          <t>N | 349呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O23" s="19" t="inlineStr">
-        <is>
-          <t>P | 273呎 (1房)
-$553万
-$20,268/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="P23" s="19" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$548万
-$20,057/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-$1,285万
-$25,094/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 397呎 (3房)
-$971万
-$24,469/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$861万
-$24,606/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$863万
-$24,666/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$860万
-$24,718/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>F | 348呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H24" s="19" t="inlineStr">
-        <is>
-          <t>G | 348呎 (2房)
-$767万
-$22,037/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I24" s="19" t="inlineStr">
-        <is>
-          <t>H | 348呎 (2房)
-$769万
-$22,089/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J24" s="17" t="inlineStr">
-        <is>
-          <t>J | 464呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K24" s="19" t="inlineStr">
-        <is>
-          <t>K | 395呎 (3房)
-$809万
-$20,493/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L24" s="19" t="inlineStr">
-        <is>
-          <t>L | 270呎 (1房)
-$562万
-$20,798/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M24" s="19" t="inlineStr">
-        <is>
-          <t>M | 265呎 (1房)
-$530万
-$19,990/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N24" s="17" t="inlineStr">
-        <is>
-          <t>N | 349呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O24" s="19" t="inlineStr">
-        <is>
-          <t>P | 273呎 (1房)
-$579万
-$21,199/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="P24" s="19" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$573万
-$20,973/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>B | 397呎 (3房)
-$850万
-$21,401/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D25" s="19" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$691万
-$19,746/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E25" s="19" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$693万
-$19,795/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F25" s="19" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$690万
-$19,836/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>F | 348呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H25" s="19" t="inlineStr">
-        <is>
-          <t>G | 348呎 (2房)
-$745万
-$21,422/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I25" s="19" t="inlineStr">
-        <is>
-          <t>H | 348呎 (2房)
-$760万
-$21,831/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J25" s="17" t="inlineStr">
-        <is>
-          <t>J | 464呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K25" s="19" t="inlineStr">
-        <is>
-          <t>K | 395呎 (3房)
-$804万
-$20,365/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L25" s="19" t="inlineStr">
-        <is>
-          <t>L | 270呎 (1房)
-$566万
-$20,953/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M25" s="19" t="inlineStr">
-        <is>
-          <t>M | 265呎 (1房)
-$528万
-$19,932/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="N25" s="17" t="inlineStr">
-        <is>
-          <t>N | 349呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O25" s="19" t="inlineStr">
-        <is>
-          <t>P | 273呎 (1房)
-$547万
-$20,021/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="P25" s="19" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$541万
-$19,810/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 397呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$684万
-$19,556/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E26" s="19" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$686万
-$19,605/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F26" s="19" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$684万
-$19,645/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G26" s="19" t="inlineStr">
-        <is>
-          <t>F | 348呎 (2房)
-$788万
-$22,650/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>G | 348呎 (2房)
-$832万
-$23,899/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>H | 348呎 (2房)
-$834万
-$23,960/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J26" s="17" t="inlineStr">
-        <is>
-          <t>J | 464呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K26" s="19" t="inlineStr">
-        <is>
-          <t>K | 395呎 (3房)
-$794万
-$20,110/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L26" s="19" t="inlineStr">
-        <is>
-          <t>L | 270呎 (1房)
-$529万
-$19,587/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M26" s="19" t="inlineStr">
-        <is>
-          <t>M | 265呎 (1房)
-$527万
-$19,871/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="N26" s="17" t="inlineStr">
-        <is>
-          <t>N | 349呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O26" s="19" t="inlineStr">
-        <is>
-          <t>P | 273呎 (1房)
-$575万
-$21,067/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="P26" s="19" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$539万
-$19,747/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>B | 397呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D27" s="19" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$680万
-$19,430/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E27" s="19" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$682万
-$19,479/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F27" s="19" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$679万
-$19,518/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>F | 348呎 (2房)
-$824万
-$23,687/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>G | 348呎 (2房)
-$826万
-$23,747/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>H | 348呎 (2房)
-$828万
-$23,805/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J27" s="17" t="inlineStr">
-        <is>
-          <t>J | 464呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K27" s="19" t="inlineStr">
-        <is>
-          <t>K | 395呎 (3房)
-$779万
-$19,729/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L27" s="19" t="inlineStr">
-        <is>
-          <t>L | 270呎 (1房)
-$555万
-$20,566/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M27" s="19" t="inlineStr">
-        <is>
-          <t>M | 265呎 (1房)
-$553万
-$20,864/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="N27" s="17" t="inlineStr">
-        <is>
-          <t>N | 349呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O27" s="19" t="inlineStr">
-        <is>
-          <t>P | 273呎 (1房)
-$543万
-$19,899/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="P27" s="19" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$537万
-$19,685/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-$1,081万
-$21,117/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>B | 397呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D28" s="19" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$713万
-$20,376/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E28" s="19" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$677万
-$19,353/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F28" s="19" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$712万
-$20,469/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>F | 348呎 (2房)
-$819万
-$23,532/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H28" s="19" t="inlineStr">
-        <is>
-          <t>G | 348呎 (2房)
-$739万
-$21,233/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I28" s="19" t="inlineStr">
-        <is>
-          <t>H | 348呎 (2房)
-$741万
-$21,287/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J28" s="17" t="inlineStr">
-        <is>
-          <t>J | 464呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K28" s="19" t="inlineStr">
-        <is>
-          <t>K | 395呎 (3房)
-$785万
-$19,864/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L28" s="19" t="inlineStr">
-        <is>
-          <t>L | 270呎 (1房)
-$548万
-$20,303/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M28" s="19" t="inlineStr">
-        <is>
-          <t>M | 265呎 (1房)
-$546万
-$20,598/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="N28" s="17" t="inlineStr">
-        <is>
-          <t>N | 349呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O28" s="19" t="inlineStr">
-        <is>
-          <t>P | 273呎 (1房)
-$588万
-$21,537/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="P28" s="19" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$551万
-$20,186/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-$1,201万
-$23,463/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>B | 397呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D29" s="19" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$676万
-$19,304/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E29" s="19" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$677万
-$19,353/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F29" s="19" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$675万
-$19,391/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G29" s="19" t="inlineStr">
-        <is>
-          <t>F | 348呎 (2房)
-$737万
-$21,178/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H29" s="19" t="inlineStr">
-        <is>
-          <t>G | 348呎 (2房)
-$739万
-$21,233/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I29" s="19" t="inlineStr">
-        <is>
-          <t>H | 348呎 (2房)
-$749万
-$21,524/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J29" s="17" t="inlineStr">
-        <is>
-          <t>J | 464呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K29" s="19" t="inlineStr">
-        <is>
-          <t>K | 395呎 (3房)
-$772万
-$19,538/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L29" s="19" t="inlineStr">
-        <is>
-          <t>L | 270呎 (1房)
-$548万
-$20,303/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M29" s="19" t="inlineStr">
-        <is>
-          <t>M | 265呎 (1房)
-$546万
-$20,598/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="N29" s="17" t="inlineStr">
-        <is>
-          <t>N | 349呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O29" s="19" t="inlineStr">
-        <is>
-          <t>P | 273呎 (1房)
-$557万
-$20,403/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="P29" s="19" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$554万
-$20,298/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B30" s="19" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-$993万
-$19,392/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>B | 397呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D30" s="19" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$716万
-$20,471/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E30" s="19" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$718万
-$20,523/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F30" s="19" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$716万
-$20,563/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G30" s="19" t="inlineStr">
-        <is>
-          <t>F | 348呎 (2房)
-$727万
-$20,902/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H30" s="19" t="inlineStr">
-        <is>
-          <t>G | 348呎 (2房)
-$729万
-$20,956/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I30" s="19" t="inlineStr">
-        <is>
-          <t>H | 348呎 (2房)
-$731万
-$21,010/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J30" s="19" t="inlineStr">
-        <is>
-          <t>J | 464呎 (3房)
-$928万
-$19,990/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K30" s="19" t="inlineStr">
-        <is>
-          <t>K | 395呎 (3房)
-$761万
-$19,262/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L30" s="19" t="inlineStr">
-        <is>
-          <t>L | 270呎 (1房)
-$545万
-$20,180/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M30" s="19" t="inlineStr">
-        <is>
-          <t>M | 265呎 (1房)
-$543万
-$20,486/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="N30" s="17" t="inlineStr">
-        <is>
-          <t>N | 349呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O30" s="19" t="inlineStr">
-        <is>
-          <t>P | 273呎 (1房)
-$554万
-$20,275/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="P30" s="19" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$579万
-$21,220/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-$983万
-$19,199/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C31" s="19" t="inlineStr">
-        <is>
-          <t>B | 397呎 (3房)
-$811万
-$20,435/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D31" s="19" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$713万
-$20,378/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E31" s="19" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$751万
-$21,448/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F31" s="19" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$708万
-$20,359/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G31" s="19" t="inlineStr">
-        <is>
-          <t>F | 348呎 (2房)
-$760万
-$21,845/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H31" s="19" t="inlineStr">
-        <is>
-          <t>G | 348呎 (2房)
-$691万
-$19,866/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="I31" s="19" t="inlineStr">
-        <is>
-          <t>H | 348呎 (2房)
-$712万
-$20,455/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J31" s="19" t="inlineStr">
-        <is>
-          <t>J | 464呎 (3房)
-$964万
-$20,777/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K31" s="19" t="inlineStr">
-        <is>
-          <t>K | 395呎 (3房)
-$816万
-$20,661/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L31" s="19" t="inlineStr">
-        <is>
-          <t>L | 270呎 (1房)
-$506万
-$18,743/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M31" s="19" t="inlineStr">
-        <is>
-          <t>M | 265呎 (1房)
-$504万
-$19,015/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N31" s="17" t="inlineStr">
-        <is>
-          <t>N | 349呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="O31" s="19" t="inlineStr">
-        <is>
-          <t>P | 273呎 (1房)
-$521万
-$19,091/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P31" s="19" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$516万
-$18,884/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B32" s="19" t="inlineStr">
-        <is>
-          <t>A | 512呎 (3房)
-$1,025万
-$20,017/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C32" s="19" t="inlineStr">
-        <is>
-          <t>B | 397呎 (3房)
-$790万
-$19,909/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D32" s="19" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
-$702万
-$20,056/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E32" s="19" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$704万
-$20,110/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F32" s="19" t="inlineStr">
-        <is>
-          <t>E | 348呎 (2房)
-$701万
-$20,147/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G32" s="19" t="inlineStr">
-        <is>
-          <t>F | 348呎 (2房)
-$703万
-$20,198/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H32" s="19" t="inlineStr">
-        <is>
-          <t>G | 348呎 (2房)
-$701万
-$20,130/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I32" s="19" t="inlineStr">
-        <is>
-          <t>H | 348呎 (2房)
-$702万
-$20,182/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="J32" s="19" t="inlineStr">
-        <is>
-          <t>J | 464呎 (3房)
-$951万
-$20,503/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="K32" s="19" t="inlineStr">
-        <is>
-          <t>K | 395呎 (3房)
-$796万
-$20,152/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="L32" s="19" t="inlineStr">
-        <is>
-          <t>L | 270呎 (1房)
-$532万
-$19,721/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M32" s="19" t="inlineStr">
-        <is>
-          <t>M | 265呎 (1房)
-$531万
-$20,029/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="N32" s="19" t="inlineStr">
-        <is>
-          <t>N | 349呎 (2房)
-$710万
-$20,358/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="O32" s="19" t="inlineStr">
-        <is>
-          <t>P | 273呎 (1房)
-$548万
-$20,089/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="P32" s="19" t="inlineStr">
-        <is>
-          <t>Q | 273呎 (1房)
-$542万
-$19,870/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>A | 513呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>B | 359呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>C | 312呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>D | 312呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="inlineStr">
-        <is>
-          <t>E | 311呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="inlineStr">
-        <is>
-          <t>F | 311呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H33" s="17" t="inlineStr">
-        <is>
-          <t>G | 311呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I33" s="17" t="inlineStr">
-        <is>
-          <t>H | 311呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J33" s="16" t="inlineStr">
-        <is>
-          <t>J | 426呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="K33" s="16" t="inlineStr">
-        <is>
-          <t>K | 357呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="L33" s="17" t="inlineStr">
-        <is>
-          <t>L | 232呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="M33" s="16" t="inlineStr">
-        <is>
-          <t>M | 564呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="N33" s="16" t="inlineStr">
-        <is>
-          <t>N | 236呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="O33" s="16" t="inlineStr">
-        <is>
-          <t>P | 236呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="P33" s="18" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-马头角-壹沐第2期.xlsx
+++ b/files/九龙-马头角-壹沐第2期.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +142,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +223,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +653,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -19943,4 +20122,3714 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M4" s="19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N4" s="19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O4" s="19" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P4" s="19" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 684呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 269呎 (1房)
+$816万
+$30,346/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$1052万
+$30,063/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 348呎 (2房)
+$1049万
+$30,144/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$1051万
+$30,207/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 957呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 270呎 (1房)
+$726万
+$26,889/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>H | 265呎 (1房)
+$723万
+$27,294/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t>J | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K5" s="20" t="inlineStr">
+        <is>
+          <t>K | 273呎 (1房)
+$751万
+$27,498/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>L | 273呎 (1房)
+$745万
+$27,275/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="M5" s="22" t="inlineStr"/>
+      <c r="N5" s="22" t="inlineStr"/>
+      <c r="O5" s="22" t="inlineStr"/>
+      <c r="P5" s="22" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+$1471万
+$28,729/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 397呎 (3房)
+$1130万
+$28,458/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$911万
+$26,030/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$913万
+$26,084/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$862万
+$24,778/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>F | 348呎 (2房)
+$901万
+$25,893/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>G | 348呎 (2房)
+$853万
+$24,517/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>H | 348呎 (2房)
+$810万
+$23,276/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t>J | 464呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>K | 395呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L6" s="23" t="inlineStr">
+        <is>
+          <t>L | 270呎 (1房)
+$548万
+$20,300/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M6" s="23" t="inlineStr">
+        <is>
+          <t>M | 265呎 (1房)
+$546万
+$20,605/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t>N | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O6" s="23" t="inlineStr">
+        <is>
+          <t>P | 273呎 (1房)
+$567万
+$20,763/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P6" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$561万
+$20,565/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+$1196万
+$23,368/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>B | 397呎 (3房)
+$906万
+$22,831/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$803万
+$22,929/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$804万
+$22,978/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$802万
+$23,038/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 348呎 (2房)
+$958万
+$27,537/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 348呎 (2房)
+$959万
+$27,546/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>H | 348呎 (2房)
+$961万
+$27,606/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>J | 464呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
+        <is>
+          <t>K | 395呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L7" s="23" t="inlineStr">
+        <is>
+          <t>L | 270呎 (1房)
+$525万
+$19,430/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M7" s="23" t="inlineStr">
+        <is>
+          <t>M | 265呎 (1房)
+$552万
+$20,814/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="N7" s="21" t="inlineStr">
+        <is>
+          <t>N | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O7" s="23" t="inlineStr">
+        <is>
+          <t>P | 273呎 (1房)
+$542万
+$19,840/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P7" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$536万
+$19,642/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+$1190万
+$23,237/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>B | 397呎 (3房)
+$901万
+$22,702/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$811万
+$23,181/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$844万
+$24,119/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$797万
+$22,909/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>F | 348呎 (2房)
+$858万
+$24,644/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 348呎 (2房)
+$953万
+$27,391/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>H | 348呎 (2房)
+$955万
+$27,451/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t>J | 464呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K8" s="21" t="inlineStr">
+        <is>
+          <t>K | 395呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L8" s="23" t="inlineStr">
+        <is>
+          <t>L | 270呎 (1房)
+$523万
+$19,373/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M8" s="23" t="inlineStr">
+        <is>
+          <t>M | 265呎 (1房)
+$521万
+$19,661/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N8" s="21" t="inlineStr">
+        <is>
+          <t>N | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O8" s="23" t="inlineStr">
+        <is>
+          <t>P | 273呎 (1房)
+$543万
+$19,893/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P8" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$535万
+$19,586/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+$1218万
+$23,783/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>B | 397呎 (3房)
+$946万
+$23,829/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$794万
+$22,672/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$795万
+$22,724/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$837万
+$24,045/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 348呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 348呎 (2房)
+$948万
+$27,239/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>H | 348呎 (2房)
+$950万
+$27,299/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>J | 464呎 (3房)
+$1306万
+$28,157/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>K | 395呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L9" s="23" t="inlineStr">
+        <is>
+          <t>L | 270呎 (1房)
+$522万
+$19,320/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M9" s="23" t="inlineStr">
+        <is>
+          <t>M | 265呎 (1房)
+$520万
+$19,606/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t>N | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O9" s="23" t="inlineStr">
+        <is>
+          <t>P | 273呎 (1房)
+$538万
+$19,724/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P9" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$533万
+$19,526/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+$1211万
+$23,648/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>B | 397呎 (3房)
+$954万
+$24,029/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$833万
+$23,796/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$835万
+$23,850/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$788万
+$22,650/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 348呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t>G | 348呎 (2房)
+$761万
+$21,861/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
+        <is>
+          <t>H | 348呎 (2房)
+$805万
+$23,128/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>J | 464呎 (3房)
+$1299万
+$28,000/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="inlineStr">
+        <is>
+          <t>K | 395呎 (3房)
+$1059万
+$26,810/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L10" s="23" t="inlineStr">
+        <is>
+          <t>L | 270呎 (1房)
+$523万
+$19,374/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M10" s="23" t="inlineStr">
+        <is>
+          <t>M | 265呎 (1房)
+$547万
+$20,638/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N10" s="21" t="inlineStr">
+        <is>
+          <t>N | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O10" s="23" t="inlineStr">
+        <is>
+          <t>P | 273呎 (1房)
+$537万
+$19,668/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P10" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$534万
+$19,578/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+$1161万
+$22,671/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 397呎 (3房)
+$1048万
+$26,406/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$812万
+$23,207/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$828万
+$23,646/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$816万
+$23,444/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 348呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H11" s="23" t="inlineStr">
+        <is>
+          <t>G | 348呎 (2房)
+$761万
+$21,861/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I11" s="23" t="inlineStr">
+        <is>
+          <t>H | 348呎 (2房)
+$813万
+$23,371/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t>J | 464呎 (3房)
+$1133万
+$24,417/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="inlineStr">
+        <is>
+          <t>K | 395呎 (3房)
+$1059万
+$26,810/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L11" s="23" t="inlineStr">
+        <is>
+          <t>L | 270呎 (1房)
+$523万
+$19,374/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M11" s="23" t="inlineStr">
+        <is>
+          <t>M | 265呎 (1房)
+$518万
+$19,552/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N11" s="21" t="inlineStr">
+        <is>
+          <t>N | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O11" s="20" t="inlineStr">
+        <is>
+          <t>P | 273呎 (1房)
+$674万
+$24,696/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="P11" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$601万
+$22,002/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+$1148万
+$22,412/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>B | 397呎 (3房)
+$933万
+$23,491/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$807万
+$23,070/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$805万
+$22,994/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$802万
+$23,051/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 348呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t>G | 348呎 (2房)
+$752万
+$21,613/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I12" s="23" t="inlineStr">
+        <is>
+          <t>H | 348呎 (2房)
+$804万
+$23,106/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J12" s="23" t="inlineStr">
+        <is>
+          <t>J | 464呎 (3房)
+$1061万
+$22,872/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K12" s="20" t="inlineStr">
+        <is>
+          <t>K | 395呎 (3房)
+$1032万
+$26,139/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L12" s="23" t="inlineStr">
+        <is>
+          <t>L | 270呎 (1房)
+$517万
+$19,157/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M12" s="23" t="inlineStr">
+        <is>
+          <t>M | 265呎 (1房)
+$544万
+$20,520/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t>N | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O12" s="20" t="inlineStr">
+        <is>
+          <t>P | 273呎 (1房)
+$670万
+$24,549/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="P12" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$597万
+$21,870/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+$1141万
+$22,282/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>B | 397呎 (3房)
+$927万
+$23,355/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$798万
+$22,811/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$800万
+$22,860/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$797万
+$22,916/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 348呎 (2房)
+$926万
+$26,612/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H13" s="23" t="inlineStr">
+        <is>
+          <t>G | 348呎 (2房)
+$824万
+$23,677/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I13" s="23" t="inlineStr">
+        <is>
+          <t>H | 348呎 (2房)
+$799万
+$22,974/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="inlineStr">
+        <is>
+          <t>J | 464呎 (3房)
+$1055万
+$22,742/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K13" s="20" t="inlineStr">
+        <is>
+          <t>K | 395呎 (3房)
+$1026万
+$25,987/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L13" s="23" t="inlineStr">
+        <is>
+          <t>L | 270呎 (1房)
+$583万
+$21,583/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M13" s="23" t="inlineStr">
+        <is>
+          <t>M | 265呎 (1房)
+$580万
+$21,906/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="N13" s="21" t="inlineStr">
+        <is>
+          <t>N | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O13" s="20" t="inlineStr">
+        <is>
+          <t>P | 273呎 (1房)
+$668万
+$24,480/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="P13" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$595万
+$21,808/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+$1134万
+$22,152/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 397呎 (3房)
+$973万
+$24,509/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$794万
+$22,677/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$796万
+$22,729/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$797万
+$22,911/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 348呎 (2房)
+$921万
+$26,460/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H14" s="23" t="inlineStr">
+        <is>
+          <t>G | 348呎 (2房)
+$819万
+$23,540/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I14" s="23" t="inlineStr">
+        <is>
+          <t>H | 348呎 (2房)
+$821万
+$23,594/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J14" s="23" t="inlineStr">
+        <is>
+          <t>J | 464呎 (3房)
+$1107万
+$23,867/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K14" s="20" t="inlineStr">
+        <is>
+          <t>K | 395呎 (3房)
+$1020万
+$25,835/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L14" s="23" t="inlineStr">
+        <is>
+          <t>L | 270呎 (1房)
+$581万
+$21,523/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="M14" s="23" t="inlineStr">
+        <is>
+          <t>M | 265呎 (1房)
+$579万
+$21,841/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="N14" s="21" t="inlineStr">
+        <is>
+          <t>N | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O14" s="20" t="inlineStr">
+        <is>
+          <t>P | 273呎 (1房)
+$666万
+$24,403/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="P14" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$594万
+$21,742/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+$1126万
+$21,987/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>B | 397呎 (3房)
+$891万
+$22,443/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$789万
+$22,546/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$835万
+$23,853/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$788万
+$22,650/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>F | 348呎 (2房)
+$824万
+$23,674/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H15" s="23" t="inlineStr">
+        <is>
+          <t>G | 348呎 (2房)
+$814万
+$23,403/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>H | 348呎 (2房)
+$907万
+$26,063/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J15" s="23" t="inlineStr">
+        <is>
+          <t>J | 464呎 (3房)
+$1043万
+$22,481/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K15" s="20" t="inlineStr">
+        <is>
+          <t>K | 395呎 (3房)
+$1014万
+$25,684/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L15" s="23" t="inlineStr">
+        <is>
+          <t>L | 270呎 (1房)
+$580万
+$21,463/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="M15" s="23" t="inlineStr">
+        <is>
+          <t>M | 265呎 (1房)
+$609万
+$22,990/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="N15" s="21" t="inlineStr">
+        <is>
+          <t>N | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O15" s="23" t="inlineStr">
+        <is>
+          <t>P | 273呎 (1房)
+$529万
+$19,381/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="P15" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$524万
+$19,184/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+$1136万
+$22,184/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>B | 397呎 (3房)
+$860万
+$21,675/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$793万
+$22,645/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$794万
+$22,697/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$792万
+$22,751/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 348呎 (2房)
+$910万
+$26,152/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>G | 348呎 (2房)
+$810万
+$23,266/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I16" s="23" t="inlineStr">
+        <is>
+          <t>H | 348呎 (2房)
+$812万
+$23,320/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J16" s="23" t="inlineStr">
+        <is>
+          <t>J | 464呎 (3房)
+$1084万
+$23,352/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K16" s="23" t="inlineStr">
+        <is>
+          <t>K | 395呎 (3房)
+$845万
+$21,384/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L16" s="23" t="inlineStr">
+        <is>
+          <t>L | 270呎 (1房)
+$511万
+$18,937/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M16" s="23" t="inlineStr">
+        <is>
+          <t>M | 265呎 (1房)
+$575万
+$21,715/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="N16" s="21" t="inlineStr">
+        <is>
+          <t>N | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O16" s="23" t="inlineStr">
+        <is>
+          <t>P | 273呎 (1房)
+$527万
+$19,322/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="P16" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$522万
+$19,124/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+$1129万
+$22,052/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>B | 397呎 (3房)
+$855万
+$21,546/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$746万
+$21,327/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$790万
+$22,564/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$746万
+$21,427/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>F | 348呎 (2房)
+$814万
+$23,397/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H17" s="23" t="inlineStr">
+        <is>
+          <t>G | 348呎 (2房)
+$850万
+$24,416/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I17" s="23" t="inlineStr">
+        <is>
+          <t>H | 348呎 (2房)
+$807万
+$23,183/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J17" s="23" t="inlineStr">
+        <is>
+          <t>J | 464呎 (3房)
+$1077万
+$23,214/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K17" s="23" t="inlineStr">
+        <is>
+          <t>K | 395呎 (3房)
+$882万
+$22,332/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L17" s="23" t="inlineStr">
+        <is>
+          <t>L | 270呎 (1房)
+$538万
+$19,932/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M17" s="23" t="inlineStr">
+        <is>
+          <t>M | 265呎 (1房)
+$508万
+$19,162/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N17" s="21" t="inlineStr">
+        <is>
+          <t>N | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O17" s="23" t="inlineStr">
+        <is>
+          <t>P | 273呎 (1房)
+$555万
+$20,336/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P17" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$521万
+$19,068/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+$1256万
+$24,537/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 397呎 (3房)
+$850万
+$21,416/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$783万
+$22,379/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$744万
+$21,250/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$741万
+$21,300/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 348呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>G | 348呎 (2房)
+$800万
+$22,994/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
+        <is>
+          <t>H | 348呎 (2房)
+$847万
+$24,326/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>J | 464呎 (3房)
+$1241万
+$26,741/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K18" s="23" t="inlineStr">
+        <is>
+          <t>K | 395呎 (3房)
+$872万
+$22,074/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L18" s="23" t="inlineStr">
+        <is>
+          <t>L | 270呎 (1房)
+$509万
+$18,863/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M18" s="23" t="inlineStr">
+        <is>
+          <t>M | 265呎 (1房)
+$534万
+$20,169/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N18" s="21" t="inlineStr">
+        <is>
+          <t>N | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O18" s="23" t="inlineStr">
+        <is>
+          <t>P | 273呎 (1房)
+$553万
+$20,274/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P18" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$519万
+$19,009/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+$1183万
+$23,105/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>B | 397呎 (3房)
+$845万
+$21,287/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$738万
+$21,075/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$739万
+$21,124/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$737万
+$21,173/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 348呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H19" s="23" t="inlineStr">
+        <is>
+          <t>G | 348呎 (2房)
+$795万
+$22,857/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I19" s="23" t="inlineStr">
+        <is>
+          <t>H | 348呎 (2房)
+$797万
+$22,909/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>J | 464呎 (3房)
+$1234万
+$26,584/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="K19" s="23" t="inlineStr">
+        <is>
+          <t>K | 395呎 (3房)
+$867万
+$21,942/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L19" s="23" t="inlineStr">
+        <is>
+          <t>L | 270呎 (1房)
+$536万
+$19,866/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M19" s="23" t="inlineStr">
+        <is>
+          <t>M | 265呎 (1房)
+$503万
+$18,995/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="N19" s="21" t="inlineStr">
+        <is>
+          <t>N | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O19" s="23" t="inlineStr">
+        <is>
+          <t>P | 273呎 (1房)
+$521万
+$19,095/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P19" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$545万
+$19,947/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+$1333万
+$26,035/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>B | 397呎 (3房)
+$870万
+$21,906/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$893万
+$25,526/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$895万
+$25,583/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$892万
+$25,644/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 348呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H20" s="23" t="inlineStr">
+        <is>
+          <t>G | 348呎 (2房)
+$795万
+$22,857/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I20" s="23" t="inlineStr">
+        <is>
+          <t>H | 348呎 (2房)
+$797万
+$22,909/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J20" s="21" t="inlineStr">
+        <is>
+          <t>J | 464呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K20" s="23" t="inlineStr">
+        <is>
+          <t>K | 395呎 (3房)
+$876万
+$22,186/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L20" s="23" t="inlineStr">
+        <is>
+          <t>L | 270呎 (1房)
+$508万
+$18,800/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M20" s="23" t="inlineStr">
+        <is>
+          <t>M | 265呎 (1房)
+$503万
+$18,995/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="N20" s="21" t="inlineStr">
+        <is>
+          <t>N | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O20" s="23" t="inlineStr">
+        <is>
+          <t>P | 273呎 (1房)
+$521万
+$19,095/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P20" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$516万
+$18,897/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+$1251万
+$24,437/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>B | 397呎 (3房)
+$896万
+$22,575/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$794万
+$22,695/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$796万
+$22,747/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$793万
+$22,800/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 348呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H21" s="23" t="inlineStr">
+        <is>
+          <t>G | 348呎 (2房)
+$786万
+$22,583/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I21" s="23" t="inlineStr">
+        <is>
+          <t>H | 348呎 (2房)
+$788万
+$22,637/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J21" s="21" t="inlineStr">
+        <is>
+          <t>J | 464呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K21" s="23" t="inlineStr">
+        <is>
+          <t>K | 395呎 (3房)
+$856万
+$21,675/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L21" s="23" t="inlineStr">
+        <is>
+          <t>L | 270呎 (1房)
+$568万
+$21,044/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M21" s="23" t="inlineStr">
+        <is>
+          <t>M | 265呎 (1房)
+$501万
+$18,917/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N21" s="21" t="inlineStr">
+        <is>
+          <t>N | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O21" s="23" t="inlineStr">
+        <is>
+          <t>P | 273呎 (1房)
+$518万
+$18,979/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="P21" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$514万
+$18,814/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+$1309万
+$25,564/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 397呎 (3房)
+$990万
+$24,929/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$877万
+$25,063/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$879万
+$25,123/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$876万
+$25,181/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 348呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>G | 348呎 (2房)
+$794万
+$22,820/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I22" s="23" t="inlineStr">
+        <is>
+          <t>H | 348呎 (2房)
+$792万
+$22,750/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J22" s="21" t="inlineStr">
+        <is>
+          <t>J | 464呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K22" s="23" t="inlineStr">
+        <is>
+          <t>K | 395呎 (3房)
+$924万
+$23,387/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L22" s="23" t="inlineStr">
+        <is>
+          <t>L | 270呎 (1房)
+$537万
+$19,877/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M22" s="23" t="inlineStr">
+        <is>
+          <t>M | 265呎 (1房)
+$535万
+$20,170/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N22" s="21" t="inlineStr">
+        <is>
+          <t>N | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O22" s="23" t="inlineStr">
+        <is>
+          <t>P | 273呎 (1房)
+$553万
+$20,268/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="P22" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$548万
+$20,057/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+$1285万
+$25,094/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 397呎 (3房)
+$971万
+$24,469/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$861万
+$24,606/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$863万
+$24,666/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$860万
+$24,718/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 348呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H23" s="23" t="inlineStr">
+        <is>
+          <t>G | 348呎 (2房)
+$767万
+$22,037/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I23" s="23" t="inlineStr">
+        <is>
+          <t>H | 348呎 (2房)
+$769万
+$22,089/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J23" s="21" t="inlineStr">
+        <is>
+          <t>J | 464呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K23" s="23" t="inlineStr">
+        <is>
+          <t>K | 395呎 (3房)
+$809万
+$20,493/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L23" s="23" t="inlineStr">
+        <is>
+          <t>L | 270呎 (1房)
+$562万
+$20,798/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M23" s="23" t="inlineStr">
+        <is>
+          <t>M | 265呎 (1房)
+$530万
+$19,990/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N23" s="21" t="inlineStr">
+        <is>
+          <t>N | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O23" s="23" t="inlineStr">
+        <is>
+          <t>P | 273呎 (1房)
+$579万
+$21,199/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="P23" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$573万
+$20,973/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>B | 397呎 (3房)
+$850万
+$21,401/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$691万
+$19,746/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$693万
+$19,795/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$690万
+$19,836/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 348呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>G | 348呎 (2房)
+$745万
+$21,422/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I24" s="23" t="inlineStr">
+        <is>
+          <t>H | 348呎 (2房)
+$760万
+$21,831/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J24" s="21" t="inlineStr">
+        <is>
+          <t>J | 464呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K24" s="23" t="inlineStr">
+        <is>
+          <t>K | 395呎 (3房)
+$804万
+$20,365/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L24" s="23" t="inlineStr">
+        <is>
+          <t>L | 270呎 (1房)
+$566万
+$20,953/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M24" s="23" t="inlineStr">
+        <is>
+          <t>M | 265呎 (1房)
+$528万
+$19,932/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="N24" s="21" t="inlineStr">
+        <is>
+          <t>N | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O24" s="23" t="inlineStr">
+        <is>
+          <t>P | 273呎 (1房)
+$547万
+$20,021/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="P24" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$541万
+$19,810/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 397呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$684万
+$19,556/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$686万
+$19,605/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$684万
+$19,645/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>F | 348呎 (2房)
+$788万
+$22,650/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>G | 348呎 (2房)
+$832万
+$23,899/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>H | 348呎 (2房)
+$834万
+$23,960/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J25" s="21" t="inlineStr">
+        <is>
+          <t>J | 464呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K25" s="23" t="inlineStr">
+        <is>
+          <t>K | 395呎 (3房)
+$794万
+$20,110/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L25" s="23" t="inlineStr">
+        <is>
+          <t>L | 270呎 (1房)
+$529万
+$19,587/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M25" s="23" t="inlineStr">
+        <is>
+          <t>M | 265呎 (1房)
+$527万
+$19,871/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="N25" s="21" t="inlineStr">
+        <is>
+          <t>N | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O25" s="23" t="inlineStr">
+        <is>
+          <t>P | 273呎 (1房)
+$575万
+$21,067/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="P25" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$539万
+$19,747/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 397呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$680万
+$19,430/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$682万
+$19,479/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$679万
+$19,518/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>F | 348呎 (2房)
+$824万
+$23,687/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>G | 348呎 (2房)
+$826万
+$23,747/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I26" s="20" t="inlineStr">
+        <is>
+          <t>H | 348呎 (2房)
+$828万
+$23,805/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>J | 464呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K26" s="23" t="inlineStr">
+        <is>
+          <t>K | 395呎 (3房)
+$779万
+$19,729/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L26" s="23" t="inlineStr">
+        <is>
+          <t>L | 270呎 (1房)
+$555万
+$20,566/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M26" s="23" t="inlineStr">
+        <is>
+          <t>M | 265呎 (1房)
+$553万
+$20,864/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="N26" s="21" t="inlineStr">
+        <is>
+          <t>N | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O26" s="23" t="inlineStr">
+        <is>
+          <t>P | 273呎 (1房)
+$543万
+$19,899/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="P26" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$537万
+$19,685/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+$1081万
+$21,117/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 397呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$713万
+$20,376/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$677万
+$19,353/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$712万
+$20,469/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>F | 348呎 (2房)
+$819万
+$23,532/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H27" s="23" t="inlineStr">
+        <is>
+          <t>G | 348呎 (2房)
+$739万
+$21,233/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I27" s="23" t="inlineStr">
+        <is>
+          <t>H | 348呎 (2房)
+$741万
+$21,287/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>J | 464呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K27" s="23" t="inlineStr">
+        <is>
+          <t>K | 395呎 (3房)
+$785万
+$19,864/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L27" s="23" t="inlineStr">
+        <is>
+          <t>L | 270呎 (1房)
+$548万
+$20,303/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M27" s="23" t="inlineStr">
+        <is>
+          <t>M | 265呎 (1房)
+$546万
+$20,598/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="N27" s="21" t="inlineStr">
+        <is>
+          <t>N | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O27" s="23" t="inlineStr">
+        <is>
+          <t>P | 273呎 (1房)
+$588万
+$21,537/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="P27" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$551万
+$20,186/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+$1201万
+$23,463/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>B | 397呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$676万
+$19,304/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$677万
+$19,353/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$675万
+$19,391/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G28" s="23" t="inlineStr">
+        <is>
+          <t>F | 348呎 (2房)
+$737万
+$21,178/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H28" s="23" t="inlineStr">
+        <is>
+          <t>G | 348呎 (2房)
+$739万
+$21,233/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I28" s="23" t="inlineStr">
+        <is>
+          <t>H | 348呎 (2房)
+$749万
+$21,524/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J28" s="21" t="inlineStr">
+        <is>
+          <t>J | 464呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K28" s="23" t="inlineStr">
+        <is>
+          <t>K | 395呎 (3房)
+$772万
+$19,538/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L28" s="23" t="inlineStr">
+        <is>
+          <t>L | 270呎 (1房)
+$548万
+$20,303/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M28" s="23" t="inlineStr">
+        <is>
+          <t>M | 265呎 (1房)
+$546万
+$20,598/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="N28" s="21" t="inlineStr">
+        <is>
+          <t>N | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O28" s="23" t="inlineStr">
+        <is>
+          <t>P | 273呎 (1房)
+$557万
+$20,403/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="P28" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$554万
+$20,298/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+$993万
+$19,392/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>B | 397呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$716万
+$20,471/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$718万
+$20,523/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$716万
+$20,563/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="inlineStr">
+        <is>
+          <t>F | 348呎 (2房)
+$727万
+$20,902/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H29" s="23" t="inlineStr">
+        <is>
+          <t>G | 348呎 (2房)
+$729万
+$20,956/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I29" s="23" t="inlineStr">
+        <is>
+          <t>H | 348呎 (2房)
+$731万
+$21,010/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J29" s="23" t="inlineStr">
+        <is>
+          <t>J | 464呎 (3房)
+$928万
+$19,990/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K29" s="23" t="inlineStr">
+        <is>
+          <t>K | 395呎 (3房)
+$761万
+$19,262/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L29" s="23" t="inlineStr">
+        <is>
+          <t>L | 270呎 (1房)
+$545万
+$20,180/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M29" s="23" t="inlineStr">
+        <is>
+          <t>M | 265呎 (1房)
+$543万
+$20,486/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="N29" s="21" t="inlineStr">
+        <is>
+          <t>N | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O29" s="23" t="inlineStr">
+        <is>
+          <t>P | 273呎 (1房)
+$554万
+$20,275/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="P29" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$579万
+$21,220/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+$983万
+$19,199/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>B | 397呎 (3房)
+$811万
+$20,435/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$713万
+$20,378/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$751万
+$21,448/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$708万
+$20,359/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>F | 348呎 (2房)
+$760万
+$21,845/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H30" s="23" t="inlineStr">
+        <is>
+          <t>G | 348呎 (2房)
+$691万
+$19,866/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="I30" s="23" t="inlineStr">
+        <is>
+          <t>H | 348呎 (2房)
+$712万
+$20,455/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J30" s="23" t="inlineStr">
+        <is>
+          <t>J | 464呎 (3房)
+$964万
+$20,777/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K30" s="23" t="inlineStr">
+        <is>
+          <t>K | 395呎 (3房)
+$816万
+$20,661/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L30" s="23" t="inlineStr">
+        <is>
+          <t>L | 270呎 (1房)
+$506万
+$18,743/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M30" s="23" t="inlineStr">
+        <is>
+          <t>M | 265呎 (1房)
+$504万
+$19,015/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N30" s="21" t="inlineStr">
+        <is>
+          <t>N | 349呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="O30" s="23" t="inlineStr">
+        <is>
+          <t>P | 273呎 (1房)
+$521万
+$19,091/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P30" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$516万
+$18,884/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>A | 512呎 (3房)
+$1025万
+$20,017/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>B | 397呎 (3房)
+$790万
+$19,909/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+$702万
+$20,056/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$704万
+$20,110/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>E | 348呎 (2房)
+$701万
+$20,147/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G31" s="23" t="inlineStr">
+        <is>
+          <t>F | 348呎 (2房)
+$703万
+$20,198/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H31" s="23" t="inlineStr">
+        <is>
+          <t>G | 348呎 (2房)
+$701万
+$20,130/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I31" s="23" t="inlineStr">
+        <is>
+          <t>H | 348呎 (2房)
+$702万
+$20,182/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="J31" s="23" t="inlineStr">
+        <is>
+          <t>J | 464呎 (3房)
+$951万
+$20,503/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="K31" s="23" t="inlineStr">
+        <is>
+          <t>K | 395呎 (3房)
+$796万
+$20,152/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="L31" s="23" t="inlineStr">
+        <is>
+          <t>L | 270呎 (1房)
+$532万
+$19,721/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M31" s="23" t="inlineStr">
+        <is>
+          <t>M | 265呎 (1房)
+$531万
+$20,029/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="N31" s="23" t="inlineStr">
+        <is>
+          <t>N | 349呎 (2房)
+$710万
+$20,358/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="O31" s="23" t="inlineStr">
+        <is>
+          <t>P | 273呎 (1房)
+$548万
+$20,089/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="P31" s="23" t="inlineStr">
+        <is>
+          <t>Q | 273呎 (1房)
+$542万
+$19,870/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 513呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>B | 359呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>C | 312呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
+          <t>D | 312呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t>E | 311呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="inlineStr">
+        <is>
+          <t>F | 311呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H32" s="21" t="inlineStr">
+        <is>
+          <t>G | 311呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="inlineStr">
+        <is>
+          <t>H | 311呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J32" s="20" t="inlineStr">
+        <is>
+          <t>J | 426呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="K32" s="20" t="inlineStr">
+        <is>
+          <t>K | 357呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="L32" s="21" t="inlineStr">
+        <is>
+          <t>L | 232呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="M32" s="20" t="inlineStr">
+        <is>
+          <t>M | 564呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="N32" s="20" t="inlineStr">
+        <is>
+          <t>N | 236呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="O32" s="20" t="inlineStr">
+        <is>
+          <t>P | 236呎 (1房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="P32" s="22" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-马头角-壹沐第2期.xlsx
+++ b/files/九龙-马头角-壹沐第2期.xlsx
@@ -653,7 +653,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -21542,7 +21542,7 @@
           <t>Q | 273呎 (1房)
 $594万
 $21,742/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-马头角-壹沐第2期.xlsx
+++ b/files/九龙-马头角-壹沐第2期.xlsx
@@ -653,12 +653,12 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -1350,25 +1350,25 @@
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>8163000</v>
+        <v>72240008163000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>30346</v>
+        <v>268550216219</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>10.00%</t>
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>7346700</v>
+        <v>65016007346700</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>27311</v>
+        <v>241695194597</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>現金付款計劃 (減10.0%)</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>10.00%</t>
         </is>
       </c>
       <c r="K28" s="5" t="n">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>現金付款計劃 (減10.0%)</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>10.00%</t>
         </is>
       </c>
       <c r="K238" s="5" t="n">
@@ -15628,7 +15628,7 @@
       </c>
       <c r="M238" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>現金付款計劃 (減10.0%)</t>
         </is>
       </c>
       <c r="N238" s="3" t="inlineStr">
@@ -16436,7 +16436,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -18348,25 +18348,25 @@
         </is>
       </c>
       <c r="H281" s="5" t="n">
-        <v>8612000</v>
+        <v>79010008612000</v>
       </c>
       <c r="I281" s="5" t="n">
-        <v>24606</v>
+        <v>225742881749</v>
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>10.00%</t>
         </is>
       </c>
       <c r="K281" s="5" t="n">
-        <v>7750800</v>
+        <v>71109007750800</v>
       </c>
       <c r="L281" s="5" t="n">
-        <v>22145</v>
+        <v>203168593574</v>
       </c>
       <c r="M281" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>現金付款計劃 (減10.0%)</t>
         </is>
       </c>
       <c r="N281" s="3" t="inlineStr">
@@ -20066,7 +20066,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -27293,8 +27293,8 @@
       <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 269呎 (1房)
-$816万
-$30,346/呎
+$7224000816万
+$268,550,216,219/呎
 (在售)</t>
         </is>
       </c>
@@ -29307,7 +29307,7 @@
           <t>C | 350呎 (2房)
 $794万
 $22,695/呎
-(26年-06月-19日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -29559,8 +29559,8 @@
       <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 350呎 (2房)
-$861万
-$24,606/呎
+$7901000861万
+$225,742,881,749/呎
 (在售)</t>
         </is>
       </c>
@@ -29839,7 +29839,7 @@
           <t>F | 348呎 (2房)
 $788万
 $22,650/呎
-(26年-06月-27日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">

--- a/files/九龙-马头角-壹沐第2期.xlsx
+++ b/files/九龙-马头角-壹沐第2期.xlsx
@@ -1350,25 +1350,25 @@
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>72240008163000</v>
+        <v>7224000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>268550216219</v>
+        <v>26855</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>10.00%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>65016007346700</v>
+        <v>6501600</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>241695194597</v>
+        <v>24170</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減10.0%)</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -18348,25 +18348,25 @@
         </is>
       </c>
       <c r="H281" s="5" t="n">
-        <v>79010008612000</v>
+        <v>8612000</v>
       </c>
       <c r="I281" s="5" t="n">
-        <v>225742881749</v>
+        <v>24606</v>
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
-          <t>10.00%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K281" s="5" t="n">
-        <v>71109007750800</v>
+        <v>7750800</v>
       </c>
       <c r="L281" s="5" t="n">
-        <v>203168593574</v>
+        <v>22145</v>
       </c>
       <c r="M281" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減10.0%)</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N281" s="3" t="inlineStr">

--- a/files/九龙-马头角-壹沐第2期.xlsx
+++ b/files/九龙-马头角-壹沐第2期.xlsx
@@ -654,11 +654,11 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>7224000</v>
+        <v>72240008163000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>26855</v>
+        <v>30346</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>6501600</v>
+        <v>65016007346700</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>24170</v>
+        <v>241695194597</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>10.00%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K28" s="5" t="n">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減10.0%)</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -10202,14 +10202,14 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
-        <v>6092300</v>
+        <v>5771700</v>
       </c>
       <c r="I152" s="5" t="n">
-        <v>22990</v>
+        <v>21780</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
@@ -10217,10 +10217,10 @@
         </is>
       </c>
       <c r="K152" s="5" t="n">
-        <v>6092300</v>
+        <v>5771700</v>
       </c>
       <c r="L152" s="5" t="n">
-        <v>22990</v>
+        <v>21780</v>
       </c>
       <c r="M152" s="3" t="inlineStr">
         <is>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
-          <t>10.00%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="K238" s="5" t="n">
@@ -15628,7 +15628,7 @@
       </c>
       <c r="M238" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減10.0%)</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N238" s="3" t="inlineStr">
@@ -16312,7 +16312,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16374,7 +16374,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -18348,7 +18348,7 @@
         </is>
       </c>
       <c r="H281" s="5" t="n">
-        <v>8612000</v>
+        <v>79010008612000</v>
       </c>
       <c r="I281" s="5" t="n">
         <v>24606</v>
@@ -18359,10 +18359,10 @@
         </is>
       </c>
       <c r="K281" s="5" t="n">
-        <v>7750800</v>
+        <v>71109007750800</v>
       </c>
       <c r="L281" s="5" t="n">
-        <v>22145</v>
+        <v>203168593574</v>
       </c>
       <c r="M281" s="3" t="inlineStr">
         <is>
@@ -27294,7 +27294,7 @@
         <is>
           <t>B | 269呎 (1房)
 $7224000816万
-$268,550,216,219/呎
+$30,346/呎
 (在售)</t>
         </is>
       </c>
@@ -28615,9 +28615,9 @@
       <c r="M15" s="23" t="inlineStr">
         <is>
           <t>M | 265呎 (1房)
-$609万
-$22,990/呎
-(26年-06月-17日)</t>
+$577万
+$21,780/呎
+(26年-05月-30日)</t>
         </is>
       </c>
       <c r="N15" s="21" t="inlineStr">
@@ -29315,7 +29315,7 @@
           <t>D | 350呎 (2房)
 $796万
 $22,747/呎
-(26年-06月-22日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
@@ -29323,7 +29323,7 @@
           <t>E | 348呎 (2房)
 $793万
 $22,800/呎
-(26年-06月-22日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -29560,7 +29560,7 @@
         <is>
           <t>C | 350呎 (2房)
 $7901000861万
-$225,742,881,749/呎
+$24,606/呎
 (在售)</t>
         </is>
       </c>

--- a/files/九龙-马头角-壹沐第2期.xlsx
+++ b/files/九龙-马头角-壹沐第2期.xlsx
@@ -27402,7 +27402,7 @@
           <t>C | 350呎 (2房)
 $911万
 $26,030/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -27410,7 +27410,7 @@
           <t>D | 350呎 (2房)
 $913万
 $26,084/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
@@ -27418,7 +27418,7 @@
           <t>E | 348呎 (2房)
 $862万
 $24,778/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G6" s="23" t="inlineStr">
@@ -27426,7 +27426,7 @@
           <t>F | 348呎 (2房)
 $901万
 $25,893/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
@@ -27434,7 +27434,7 @@
           <t>G | 348呎 (2房)
 $853万
 $24,517/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr">
@@ -27442,7 +27442,7 @@
           <t>H | 348呎 (2房)
 $810万
 $23,276/呎
-(26年-05月-08日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
@@ -27466,7 +27466,7 @@
           <t>L | 270呎 (1房)
 $548万
 $20,300/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M6" s="23" t="inlineStr">
@@ -27474,7 +27474,7 @@
           <t>M | 265呎 (1房)
 $546万
 $20,605/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N6" s="21" t="inlineStr">
@@ -27490,7 +27490,7 @@
           <t>P | 273呎 (1房)
 $567万
 $20,763/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P6" s="23" t="inlineStr">
@@ -27498,7 +27498,7 @@
           <t>Q | 273呎 (1房)
 $561万
 $20,565/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -27513,7 +27513,7 @@
           <t>A | 512呎 (3房)
 $1196万
 $23,368/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -27521,7 +27521,7 @@
           <t>B | 397呎 (3房)
 $906万
 $22,831/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -27529,7 +27529,7 @@
           <t>C | 350呎 (2房)
 $803万
 $22,929/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
@@ -27537,7 +27537,7 @@
           <t>D | 350呎 (2房)
 $804万
 $22,978/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
@@ -27545,7 +27545,7 @@
           <t>E | 348呎 (2房)
 $802万
 $23,038/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -27593,7 +27593,7 @@
           <t>L | 270呎 (1房)
 $525万
 $19,430/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M7" s="23" t="inlineStr">
@@ -27601,7 +27601,7 @@
           <t>M | 265呎 (1房)
 $552万
 $20,814/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="N7" s="21" t="inlineStr">
@@ -27617,7 +27617,7 @@
           <t>P | 273呎 (1房)
 $542万
 $19,840/呎
-(26年-05月-08日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P7" s="23" t="inlineStr">
@@ -27625,7 +27625,7 @@
           <t>Q | 273呎 (1房)
 $536万
 $19,642/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -27640,7 +27640,7 @@
           <t>A | 512呎 (3房)
 $1190万
 $23,237/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -27648,7 +27648,7 @@
           <t>B | 397呎 (3房)
 $901万
 $22,702/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -27656,7 +27656,7 @@
           <t>C | 350呎 (2房)
 $811万
 $23,181/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
@@ -27664,7 +27664,7 @@
           <t>D | 350呎 (2房)
 $844万
 $24,119/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -27672,7 +27672,7 @@
           <t>E | 348呎 (2房)
 $797万
 $22,909/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G8" s="23" t="inlineStr">
@@ -27680,7 +27680,7 @@
           <t>F | 348呎 (2房)
 $858万
 $24,644/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -27720,7 +27720,7 @@
           <t>L | 270呎 (1房)
 $523万
 $19,373/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M8" s="23" t="inlineStr">
@@ -27728,7 +27728,7 @@
           <t>M | 265呎 (1房)
 $521万
 $19,661/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N8" s="21" t="inlineStr">
@@ -27744,7 +27744,7 @@
           <t>P | 273呎 (1房)
 $543万
 $19,893/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P8" s="23" t="inlineStr">
@@ -27752,7 +27752,7 @@
           <t>Q | 273呎 (1房)
 $535万
 $19,586/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -27767,7 +27767,7 @@
           <t>A | 512呎 (3房)
 $1218万
 $23,783/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -27775,7 +27775,7 @@
           <t>B | 397呎 (3房)
 $946万
 $23,829/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -27783,7 +27783,7 @@
           <t>C | 350呎 (2房)
 $794万
 $22,672/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -27791,7 +27791,7 @@
           <t>D | 350呎 (2房)
 $795万
 $22,724/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
@@ -27799,7 +27799,7 @@
           <t>E | 348呎 (2房)
 $837万
 $24,045/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -27847,7 +27847,7 @@
           <t>L | 270呎 (1房)
 $522万
 $19,320/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M9" s="23" t="inlineStr">
@@ -27855,7 +27855,7 @@
           <t>M | 265呎 (1房)
 $520万
 $19,606/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N9" s="21" t="inlineStr">
@@ -27871,7 +27871,7 @@
           <t>P | 273呎 (1房)
 $538万
 $19,724/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P9" s="23" t="inlineStr">
@@ -27879,7 +27879,7 @@
           <t>Q | 273呎 (1房)
 $533万
 $19,526/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
           <t>A | 512呎 (3房)
 $1211万
 $23,648/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -27902,7 +27902,7 @@
           <t>B | 397呎 (3房)
 $954万
 $24,029/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -27910,7 +27910,7 @@
           <t>C | 350呎 (2房)
 $833万
 $23,796/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -27918,7 +27918,7 @@
           <t>D | 350呎 (2房)
 $835万
 $23,850/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -27926,7 +27926,7 @@
           <t>E | 348呎 (2房)
 $788万
 $22,650/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -27942,7 +27942,7 @@
           <t>G | 348呎 (2房)
 $761万
 $21,861/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I10" s="23" t="inlineStr">
@@ -27950,7 +27950,7 @@
           <t>H | 348呎 (2房)
 $805万
 $23,128/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -27974,7 +27974,7 @@
           <t>L | 270呎 (1房)
 $523万
 $19,374/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M10" s="23" t="inlineStr">
@@ -27982,7 +27982,7 @@
           <t>M | 265呎 (1房)
 $547万
 $20,638/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N10" s="21" t="inlineStr">
@@ -27998,7 +27998,7 @@
           <t>P | 273呎 (1房)
 $537万
 $19,668/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P10" s="23" t="inlineStr">
@@ -28006,7 +28006,7 @@
           <t>Q | 273呎 (1房)
 $534万
 $19,578/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -28021,7 +28021,7 @@
           <t>A | 512呎 (3房)
 $1161万
 $22,671/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -28037,7 +28037,7 @@
           <t>C | 350呎 (2房)
 $812万
 $23,207/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -28045,7 +28045,7 @@
           <t>D | 350呎 (2房)
 $828万
 $23,646/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
@@ -28053,7 +28053,7 @@
           <t>E | 348呎 (2房)
 $816万
 $23,444/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -28069,7 +28069,7 @@
           <t>G | 348呎 (2房)
 $761万
 $21,861/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I11" s="23" t="inlineStr">
@@ -28077,7 +28077,7 @@
           <t>H | 348呎 (2房)
 $813万
 $23,371/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J11" s="23" t="inlineStr">
@@ -28085,7 +28085,7 @@
           <t>J | 464呎 (3房)
 $1133万
 $24,417/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
@@ -28101,7 +28101,7 @@
           <t>L | 270呎 (1房)
 $523万
 $19,374/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M11" s="23" t="inlineStr">
@@ -28109,7 +28109,7 @@
           <t>M | 265呎 (1房)
 $518万
 $19,552/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N11" s="21" t="inlineStr">
@@ -28133,7 +28133,7 @@
           <t>Q | 273呎 (1房)
 $601万
 $22,002/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -28148,7 +28148,7 @@
           <t>A | 512呎 (3房)
 $1148万
 $22,412/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -28156,7 +28156,7 @@
           <t>B | 397呎 (3房)
 $933万
 $23,491/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -28164,7 +28164,7 @@
           <t>C | 350呎 (2房)
 $807万
 $23,070/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -28172,7 +28172,7 @@
           <t>D | 350呎 (2房)
 $805万
 $22,994/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
@@ -28180,7 +28180,7 @@
           <t>E | 348呎 (2房)
 $802万
 $23,051/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -28196,7 +28196,7 @@
           <t>G | 348呎 (2房)
 $752万
 $21,613/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I12" s="23" t="inlineStr">
@@ -28204,7 +28204,7 @@
           <t>H | 348呎 (2房)
 $804万
 $23,106/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J12" s="23" t="inlineStr">
@@ -28212,7 +28212,7 @@
           <t>J | 464呎 (3房)
 $1061万
 $22,872/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr">
@@ -28228,7 +28228,7 @@
           <t>L | 270呎 (1房)
 $517万
 $19,157/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M12" s="23" t="inlineStr">
@@ -28236,7 +28236,7 @@
           <t>M | 265呎 (1房)
 $544万
 $20,520/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="N12" s="21" t="inlineStr">
@@ -28260,7 +28260,7 @@
           <t>Q | 273呎 (1房)
 $597万
 $21,870/呎
-(26年-07月-02日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -28275,7 +28275,7 @@
           <t>A | 512呎 (3房)
 $1141万
 $22,282/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -28283,7 +28283,7 @@
           <t>B | 397呎 (3房)
 $927万
 $23,355/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -28291,7 +28291,7 @@
           <t>C | 350呎 (2房)
 $798万
 $22,811/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -28299,7 +28299,7 @@
           <t>D | 350呎 (2房)
 $800万
 $22,860/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
@@ -28307,7 +28307,7 @@
           <t>E | 348呎 (2房)
 $797万
 $22,916/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -28323,7 +28323,7 @@
           <t>G | 348呎 (2房)
 $824万
 $23,677/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I13" s="23" t="inlineStr">
@@ -28331,7 +28331,7 @@
           <t>H | 348呎 (2房)
 $799万
 $22,974/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J13" s="23" t="inlineStr">
@@ -28339,7 +28339,7 @@
           <t>J | 464呎 (3房)
 $1055万
 $22,742/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -28355,7 +28355,7 @@
           <t>L | 270呎 (1房)
 $583万
 $21,583/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="M13" s="23" t="inlineStr">
@@ -28363,7 +28363,7 @@
           <t>M | 265呎 (1房)
 $580万
 $21,906/呎
-(26年-06月-21日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="N13" s="21" t="inlineStr">
@@ -28387,7 +28387,7 @@
           <t>Q | 273呎 (1房)
 $595万
 $21,808/呎
-(26年-07月-02日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -28402,7 +28402,7 @@
           <t>A | 512呎 (3房)
 $1134万
 $22,152/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -28410,7 +28410,7 @@
           <t>B | 397呎 (3房)
 $973万
 $24,509/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -28418,7 +28418,7 @@
           <t>C | 350呎 (2房)
 $794万
 $22,677/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
@@ -28426,7 +28426,7 @@
           <t>D | 350呎 (2房)
 $796万
 $22,729/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F14" s="23" t="inlineStr">
@@ -28434,7 +28434,7 @@
           <t>E | 348呎 (2房)
 $797万
 $22,911/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -28450,7 +28450,7 @@
           <t>G | 348呎 (2房)
 $819万
 $23,540/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I14" s="23" t="inlineStr">
@@ -28458,7 +28458,7 @@
           <t>H | 348呎 (2房)
 $821万
 $23,594/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J14" s="23" t="inlineStr">
@@ -28466,7 +28466,7 @@
           <t>J | 464呎 (3房)
 $1107万
 $23,867/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -28482,7 +28482,7 @@
           <t>L | 270呎 (1房)
 $581万
 $21,523/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="M14" s="23" t="inlineStr">
@@ -28490,7 +28490,7 @@
           <t>M | 265呎 (1房)
 $579万
 $21,841/呎
-(26年-06月-16日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="N14" s="21" t="inlineStr">
@@ -28514,7 +28514,7 @@
           <t>Q | 273呎 (1房)
 $594万
 $21,742/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -28529,7 +28529,7 @@
           <t>A | 512呎 (3房)
 $1126万
 $21,987/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -28537,7 +28537,7 @@
           <t>B | 397呎 (3房)
 $891万
 $22,443/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -28545,7 +28545,7 @@
           <t>C | 350呎 (2房)
 $789万
 $22,546/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -28553,7 +28553,7 @@
           <t>D | 350呎 (2房)
 $835万
 $23,853/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
@@ -28561,7 +28561,7 @@
           <t>E | 348呎 (2房)
 $788万
 $22,650/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G15" s="23" t="inlineStr">
@@ -28569,7 +28569,7 @@
           <t>F | 348呎 (2房)
 $824万
 $23,674/呎
-(26年-06月-16日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H15" s="23" t="inlineStr">
@@ -28577,7 +28577,7 @@
           <t>G | 348呎 (2房)
 $814万
 $23,403/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -28593,7 +28593,7 @@
           <t>J | 464呎 (3房)
 $1043万
 $22,481/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -28609,7 +28609,7 @@
           <t>L | 270呎 (1房)
 $580万
 $21,463/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="M15" s="23" t="inlineStr">
@@ -28617,7 +28617,7 @@
           <t>M | 265呎 (1房)
 $577万
 $21,780/呎
-(26年-05月-30日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N15" s="21" t="inlineStr">
@@ -28633,7 +28633,7 @@
           <t>P | 273呎 (1房)
 $529万
 $19,381/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="P15" s="23" t="inlineStr">
@@ -28641,7 +28641,7 @@
           <t>Q | 273呎 (1房)
 $524万
 $19,184/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -28656,7 +28656,7 @@
           <t>A | 512呎 (3房)
 $1136万
 $22,184/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -28664,7 +28664,7 @@
           <t>B | 397呎 (3房)
 $860万
 $21,675/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -28672,7 +28672,7 @@
           <t>C | 350呎 (2房)
 $793万
 $22,645/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -28680,7 +28680,7 @@
           <t>D | 350呎 (2房)
 $794万
 $22,697/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
@@ -28688,7 +28688,7 @@
           <t>E | 348呎 (2房)
 $792万
 $22,751/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -28704,7 +28704,7 @@
           <t>G | 348呎 (2房)
 $810万
 $23,266/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I16" s="23" t="inlineStr">
@@ -28712,7 +28712,7 @@
           <t>H | 348呎 (2房)
 $812万
 $23,320/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J16" s="23" t="inlineStr">
@@ -28720,7 +28720,7 @@
           <t>J | 464呎 (3房)
 $1084万
 $23,352/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr">
@@ -28728,7 +28728,7 @@
           <t>K | 395呎 (3房)
 $845万
 $21,384/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L16" s="23" t="inlineStr">
@@ -28736,7 +28736,7 @@
           <t>L | 270呎 (1房)
 $511万
 $18,937/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M16" s="23" t="inlineStr">
@@ -28744,7 +28744,7 @@
           <t>M | 265呎 (1房)
 $575万
 $21,715/呎
-(26年-06月-24日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="N16" s="21" t="inlineStr">
@@ -28760,7 +28760,7 @@
           <t>P | 273呎 (1房)
 $527万
 $19,322/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="P16" s="23" t="inlineStr">
@@ -28768,7 +28768,7 @@
           <t>Q | 273呎 (1房)
 $522万
 $19,124/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -28783,7 +28783,7 @@
           <t>A | 512呎 (3房)
 $1129万
 $22,052/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -28791,7 +28791,7 @@
           <t>B | 397呎 (3房)
 $855万
 $21,546/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -28799,7 +28799,7 @@
           <t>C | 350呎 (2房)
 $746万
 $21,327/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -28807,7 +28807,7 @@
           <t>D | 350呎 (2房)
 $790万
 $22,564/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
@@ -28815,7 +28815,7 @@
           <t>E | 348呎 (2房)
 $746万
 $21,427/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G17" s="23" t="inlineStr">
@@ -28823,7 +28823,7 @@
           <t>F | 348呎 (2房)
 $814万
 $23,397/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H17" s="23" t="inlineStr">
@@ -28831,7 +28831,7 @@
           <t>G | 348呎 (2房)
 $850万
 $24,416/呎
-(26年-06月-15日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I17" s="23" t="inlineStr">
@@ -28839,7 +28839,7 @@
           <t>H | 348呎 (2房)
 $807万
 $23,183/呎
-(26年-06月-23日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J17" s="23" t="inlineStr">
@@ -28847,7 +28847,7 @@
           <t>J | 464呎 (3房)
 $1077万
 $23,214/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K17" s="23" t="inlineStr">
@@ -28855,7 +28855,7 @@
           <t>K | 395呎 (3房)
 $882万
 $22,332/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L17" s="23" t="inlineStr">
@@ -28863,7 +28863,7 @@
           <t>L | 270呎 (1房)
 $538万
 $19,932/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M17" s="23" t="inlineStr">
@@ -28871,7 +28871,7 @@
           <t>M | 265呎 (1房)
 $508万
 $19,162/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N17" s="21" t="inlineStr">
@@ -28887,7 +28887,7 @@
           <t>P | 273呎 (1房)
 $555万
 $20,336/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P17" s="23" t="inlineStr">
@@ -28895,7 +28895,7 @@
           <t>Q | 273呎 (1房)
 $521万
 $19,068/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -28910,7 +28910,7 @@
           <t>A | 512呎 (3房)
 $1256万
 $24,537/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -28918,7 +28918,7 @@
           <t>B | 397呎 (3房)
 $850万
 $21,416/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -28926,7 +28926,7 @@
           <t>C | 350呎 (2房)
 $783万
 $22,379/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -28934,7 +28934,7 @@
           <t>D | 350呎 (2房)
 $744万
 $21,250/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
@@ -28942,7 +28942,7 @@
           <t>E | 348呎 (2房)
 $741万
 $21,300/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -28958,7 +28958,7 @@
           <t>G | 348呎 (2房)
 $800万
 $22,994/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I18" s="23" t="inlineStr">
@@ -28966,7 +28966,7 @@
           <t>H | 348呎 (2房)
 $847万
 $24,326/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -28982,7 +28982,7 @@
           <t>K | 395呎 (3房)
 $872万
 $22,074/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L18" s="23" t="inlineStr">
@@ -28990,7 +28990,7 @@
           <t>L | 270呎 (1房)
 $509万
 $18,863/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M18" s="23" t="inlineStr">
@@ -28998,7 +28998,7 @@
           <t>M | 265呎 (1房)
 $534万
 $20,169/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N18" s="21" t="inlineStr">
@@ -29014,7 +29014,7 @@
           <t>P | 273呎 (1房)
 $553万
 $20,274/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P18" s="23" t="inlineStr">
@@ -29022,7 +29022,7 @@
           <t>Q | 273呎 (1房)
 $519万
 $19,009/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -29037,7 +29037,7 @@
           <t>A | 512呎 (3房)
 $1183万
 $23,105/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -29045,7 +29045,7 @@
           <t>B | 397呎 (3房)
 $845万
 $21,287/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -29053,7 +29053,7 @@
           <t>C | 350呎 (2房)
 $738万
 $21,075/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -29061,7 +29061,7 @@
           <t>D | 350呎 (2房)
 $739万
 $21,124/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
@@ -29069,7 +29069,7 @@
           <t>E | 348呎 (2房)
 $737万
 $21,173/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -29085,7 +29085,7 @@
           <t>G | 348呎 (2房)
 $795万
 $22,857/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I19" s="23" t="inlineStr">
@@ -29093,7 +29093,7 @@
           <t>H | 348呎 (2房)
 $797万
 $22,909/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -29109,7 +29109,7 @@
           <t>K | 395呎 (3房)
 $867万
 $21,942/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L19" s="23" t="inlineStr">
@@ -29117,7 +29117,7 @@
           <t>L | 270呎 (1房)
 $536万
 $19,866/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M19" s="23" t="inlineStr">
@@ -29125,7 +29125,7 @@
           <t>M | 265呎 (1房)
 $503万
 $18,995/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="N19" s="21" t="inlineStr">
@@ -29141,7 +29141,7 @@
           <t>P | 273呎 (1房)
 $521万
 $19,095/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P19" s="23" t="inlineStr">
@@ -29149,7 +29149,7 @@
           <t>Q | 273呎 (1房)
 $545万
 $19,947/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -29172,7 +29172,7 @@
           <t>B | 397呎 (3房)
 $870万
 $21,906/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -29212,7 +29212,7 @@
           <t>G | 348呎 (2房)
 $795万
 $22,857/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I20" s="23" t="inlineStr">
@@ -29220,7 +29220,7 @@
           <t>H | 348呎 (2房)
 $797万
 $22,909/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
@@ -29236,7 +29236,7 @@
           <t>K | 395呎 (3房)
 $876万
 $22,186/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L20" s="23" t="inlineStr">
@@ -29244,7 +29244,7 @@
           <t>L | 270呎 (1房)
 $508万
 $18,800/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M20" s="23" t="inlineStr">
@@ -29252,7 +29252,7 @@
           <t>M | 265呎 (1房)
 $503万
 $18,995/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="N20" s="21" t="inlineStr">
@@ -29268,7 +29268,7 @@
           <t>P | 273呎 (1房)
 $521万
 $19,095/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P20" s="23" t="inlineStr">
@@ -29276,7 +29276,7 @@
           <t>Q | 273呎 (1房)
 $516万
 $18,897/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -29291,7 +29291,7 @@
           <t>A | 512呎 (3房)
 $1251万
 $24,437/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -29299,7 +29299,7 @@
           <t>B | 397呎 (3房)
 $896万
 $22,575/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -29307,7 +29307,7 @@
           <t>C | 350呎 (2房)
 $794万
 $22,695/呎
-(26年-07月-13日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -29315,7 +29315,7 @@
           <t>D | 350呎 (2房)
 $796万
 $22,747/呎
-(26年-07月-16日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
@@ -29323,7 +29323,7 @@
           <t>E | 348呎 (2房)
 $793万
 $22,800/呎
-(26年-07月-16日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -29339,7 +29339,7 @@
           <t>G | 348呎 (2房)
 $786万
 $22,583/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I21" s="23" t="inlineStr">
@@ -29347,7 +29347,7 @@
           <t>H | 348呎 (2房)
 $788万
 $22,637/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -29363,7 +29363,7 @@
           <t>K | 395呎 (3房)
 $856万
 $21,675/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L21" s="23" t="inlineStr">
@@ -29371,7 +29371,7 @@
           <t>L | 270呎 (1房)
 $568万
 $21,044/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M21" s="23" t="inlineStr">
@@ -29379,7 +29379,7 @@
           <t>M | 265呎 (1房)
 $501万
 $18,917/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N21" s="21" t="inlineStr">
@@ -29395,7 +29395,7 @@
           <t>P | 273呎 (1房)
 $518万
 $18,979/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="P21" s="23" t="inlineStr">
@@ -29403,7 +29403,7 @@
           <t>Q | 273呎 (1房)
 $514万
 $18,814/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -29466,7 +29466,7 @@
           <t>G | 348呎 (2房)
 $794万
 $22,820/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
@@ -29474,7 +29474,7 @@
           <t>H | 348呎 (2房)
 $792万
 $22,750/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -29490,7 +29490,7 @@
           <t>K | 395呎 (3房)
 $924万
 $23,387/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L22" s="23" t="inlineStr">
@@ -29498,7 +29498,7 @@
           <t>L | 270呎 (1房)
 $537万
 $19,877/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M22" s="23" t="inlineStr">
@@ -29506,7 +29506,7 @@
           <t>M | 265呎 (1房)
 $535万
 $20,170/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N22" s="21" t="inlineStr">
@@ -29522,7 +29522,7 @@
           <t>P | 273呎 (1房)
 $553万
 $20,268/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="P22" s="23" t="inlineStr">
@@ -29530,7 +29530,7 @@
           <t>Q | 273呎 (1房)
 $548万
 $20,057/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -29593,7 +29593,7 @@
           <t>G | 348呎 (2房)
 $767万
 $22,037/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I23" s="23" t="inlineStr">
@@ -29601,7 +29601,7 @@
           <t>H | 348呎 (2房)
 $769万
 $22,089/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -29617,7 +29617,7 @@
           <t>K | 395呎 (3房)
 $809万
 $20,493/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L23" s="23" t="inlineStr">
@@ -29625,7 +29625,7 @@
           <t>L | 270呎 (1房)
 $562万
 $20,798/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M23" s="23" t="inlineStr">
@@ -29633,7 +29633,7 @@
           <t>M | 265呎 (1房)
 $530万
 $19,990/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N23" s="21" t="inlineStr">
@@ -29649,7 +29649,7 @@
           <t>P | 273呎 (1房)
 $579万
 $21,199/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="P23" s="23" t="inlineStr">
@@ -29657,7 +29657,7 @@
           <t>Q | 273呎 (1房)
 $573万
 $20,973/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -29680,7 +29680,7 @@
           <t>B | 397呎 (3房)
 $850万
 $21,401/呎
-(26年-06月-16日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -29688,7 +29688,7 @@
           <t>C | 350呎 (2房)
 $691万
 $19,746/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
@@ -29696,7 +29696,7 @@
           <t>D | 350呎 (2房)
 $693万
 $19,795/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F24" s="23" t="inlineStr">
@@ -29704,7 +29704,7 @@
           <t>E | 348呎 (2房)
 $690万
 $19,836/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -29720,7 +29720,7 @@
           <t>G | 348呎 (2房)
 $745万
 $21,422/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I24" s="23" t="inlineStr">
@@ -29728,7 +29728,7 @@
           <t>H | 348呎 (2房)
 $760万
 $21,831/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -29744,7 +29744,7 @@
           <t>K | 395呎 (3房)
 $804万
 $20,365/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L24" s="23" t="inlineStr">
@@ -29752,7 +29752,7 @@
           <t>L | 270呎 (1房)
 $566万
 $20,953/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M24" s="23" t="inlineStr">
@@ -29760,7 +29760,7 @@
           <t>M | 265呎 (1房)
 $528万
 $19,932/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="N24" s="21" t="inlineStr">
@@ -29776,7 +29776,7 @@
           <t>P | 273呎 (1房)
 $547万
 $20,021/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="P24" s="23" t="inlineStr">
@@ -29784,7 +29784,7 @@
           <t>Q | 273呎 (1房)
 $541万
 $19,810/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -29815,7 +29815,7 @@
           <t>C | 350呎 (2房)
 $684万
 $19,556/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
@@ -29823,7 +29823,7 @@
           <t>D | 350呎 (2房)
 $686万
 $19,605/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
@@ -29831,7 +29831,7 @@
           <t>E | 348呎 (2房)
 $684万
 $19,645/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G25" s="23" t="inlineStr">
@@ -29839,7 +29839,7 @@
           <t>F | 348呎 (2房)
 $788万
 $22,650/呎
-(26年-07月-13日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -29871,7 +29871,7 @@
           <t>K | 395呎 (3房)
 $794万
 $20,110/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L25" s="23" t="inlineStr">
@@ -29879,7 +29879,7 @@
           <t>L | 270呎 (1房)
 $529万
 $19,587/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M25" s="23" t="inlineStr">
@@ -29887,7 +29887,7 @@
           <t>M | 265呎 (1房)
 $527万
 $19,871/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="N25" s="21" t="inlineStr">
@@ -29903,7 +29903,7 @@
           <t>P | 273呎 (1房)
 $575万
 $21,067/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="P25" s="23" t="inlineStr">
@@ -29911,7 +29911,7 @@
           <t>Q | 273呎 (1房)
 $539万
 $19,747/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -29942,7 +29942,7 @@
           <t>C | 350呎 (2房)
 $680万
 $19,430/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E26" s="23" t="inlineStr">
@@ -29950,7 +29950,7 @@
           <t>D | 350呎 (2房)
 $682万
 $19,479/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F26" s="23" t="inlineStr">
@@ -29958,7 +29958,7 @@
           <t>E | 348呎 (2房)
 $679万
 $19,518/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -29998,7 +29998,7 @@
           <t>K | 395呎 (3房)
 $779万
 $19,729/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L26" s="23" t="inlineStr">
@@ -30006,7 +30006,7 @@
           <t>L | 270呎 (1房)
 $555万
 $20,566/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M26" s="23" t="inlineStr">
@@ -30014,7 +30014,7 @@
           <t>M | 265呎 (1房)
 $553万
 $20,864/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="N26" s="21" t="inlineStr">
@@ -30030,7 +30030,7 @@
           <t>P | 273呎 (1房)
 $543万
 $19,899/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="P26" s="23" t="inlineStr">
@@ -30038,7 +30038,7 @@
           <t>Q | 273呎 (1房)
 $537万
 $19,685/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -30053,7 +30053,7 @@
           <t>A | 512呎 (3房)
 $1081万
 $21,117/呎
-(26年-07月-02日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -30069,7 +30069,7 @@
           <t>C | 350呎 (2房)
 $713万
 $20,376/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E27" s="23" t="inlineStr">
@@ -30077,7 +30077,7 @@
           <t>D | 350呎 (2房)
 $677万
 $19,353/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
@@ -30085,7 +30085,7 @@
           <t>E | 348呎 (2房)
 $712万
 $20,469/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -30101,7 +30101,7 @@
           <t>G | 348呎 (2房)
 $739万
 $21,233/呎
-(26年-06月-16日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I27" s="23" t="inlineStr">
@@ -30109,7 +30109,7 @@
           <t>H | 348呎 (2房)
 $741万
 $21,287/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
@@ -30125,7 +30125,7 @@
           <t>K | 395呎 (3房)
 $785万
 $19,864/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L27" s="23" t="inlineStr">
@@ -30133,7 +30133,7 @@
           <t>L | 270呎 (1房)
 $548万
 $20,303/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M27" s="23" t="inlineStr">
@@ -30141,7 +30141,7 @@
           <t>M | 265呎 (1房)
 $546万
 $20,598/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="N27" s="21" t="inlineStr">
@@ -30157,7 +30157,7 @@
           <t>P | 273呎 (1房)
 $588万
 $21,537/呎
-(26年-06月-15日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="P27" s="23" t="inlineStr">
@@ -30165,7 +30165,7 @@
           <t>Q | 273呎 (1房)
 $551万
 $20,186/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -30196,7 +30196,7 @@
           <t>C | 350呎 (2房)
 $676万
 $19,304/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E28" s="23" t="inlineStr">
@@ -30204,7 +30204,7 @@
           <t>D | 350呎 (2房)
 $677万
 $19,353/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F28" s="23" t="inlineStr">
@@ -30212,7 +30212,7 @@
           <t>E | 348呎 (2房)
 $675万
 $19,391/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
@@ -30220,7 +30220,7 @@
           <t>F | 348呎 (2房)
 $737万
 $21,178/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H28" s="23" t="inlineStr">
@@ -30228,7 +30228,7 @@
           <t>G | 348呎 (2房)
 $739万
 $21,233/呎
-(26年-06月-23日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I28" s="23" t="inlineStr">
@@ -30236,7 +30236,7 @@
           <t>H | 348呎 (2房)
 $749万
 $21,524/呎
-(26年-06月-23日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">
@@ -30252,7 +30252,7 @@
           <t>K | 395呎 (3房)
 $772万
 $19,538/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L28" s="23" t="inlineStr">
@@ -30260,7 +30260,7 @@
           <t>L | 270呎 (1房)
 $548万
 $20,303/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M28" s="23" t="inlineStr">
@@ -30268,7 +30268,7 @@
           <t>M | 265呎 (1房)
 $546万
 $20,598/呎
-(26年-06月-16日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="N28" s="21" t="inlineStr">
@@ -30284,7 +30284,7 @@
           <t>P | 273呎 (1房)
 $557万
 $20,403/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="P28" s="23" t="inlineStr">
@@ -30292,7 +30292,7 @@
           <t>Q | 273呎 (1房)
 $554万
 $20,298/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -30307,7 +30307,7 @@
           <t>A | 512呎 (3房)
 $993万
 $19,392/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
@@ -30323,7 +30323,7 @@
           <t>C | 350呎 (2房)
 $716万
 $20,471/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E29" s="23" t="inlineStr">
@@ -30331,7 +30331,7 @@
           <t>D | 350呎 (2房)
 $718万
 $20,523/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
@@ -30339,7 +30339,7 @@
           <t>E | 348呎 (2房)
 $716万
 $20,563/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
@@ -30347,7 +30347,7 @@
           <t>F | 348呎 (2房)
 $727万
 $20,902/呎
-(26年-06月-23日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H29" s="23" t="inlineStr">
@@ -30355,7 +30355,7 @@
           <t>G | 348呎 (2房)
 $729万
 $20,956/呎
-(26年-06月-14日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I29" s="23" t="inlineStr">
@@ -30363,7 +30363,7 @@
           <t>H | 348呎 (2房)
 $731万
 $21,010/呎
-(26年-06月-17日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J29" s="23" t="inlineStr">
@@ -30371,7 +30371,7 @@
           <t>J | 464呎 (3房)
 $928万
 $19,990/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K29" s="23" t="inlineStr">
@@ -30379,7 +30379,7 @@
           <t>K | 395呎 (3房)
 $761万
 $19,262/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L29" s="23" t="inlineStr">
@@ -30387,7 +30387,7 @@
           <t>L | 270呎 (1房)
 $545万
 $20,180/呎
-(26年-06月-16日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M29" s="23" t="inlineStr">
@@ -30395,7 +30395,7 @@
           <t>M | 265呎 (1房)
 $543万
 $20,486/呎
-(26年-06月-14日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="N29" s="21" t="inlineStr">
@@ -30411,7 +30411,7 @@
           <t>P | 273呎 (1房)
 $554万
 $20,275/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="P29" s="23" t="inlineStr">
@@ -30419,7 +30419,7 @@
           <t>Q | 273呎 (1房)
 $579万
 $21,220/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -30434,7 +30434,7 @@
           <t>A | 512呎 (3房)
 $983万
 $19,199/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -30442,7 +30442,7 @@
           <t>B | 397呎 (3房)
 $811万
 $20,435/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
@@ -30450,7 +30450,7 @@
           <t>C | 350呎 (2房)
 $713万
 $20,378/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
@@ -30458,7 +30458,7 @@
           <t>D | 350呎 (2房)
 $751万
 $21,448/呎
-(26年-06月-10日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F30" s="23" t="inlineStr">
@@ -30466,7 +30466,7 @@
           <t>E | 348呎 (2房)
 $708万
 $20,359/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G30" s="23" t="inlineStr">
@@ -30474,7 +30474,7 @@
           <t>F | 348呎 (2房)
 $760万
 $21,845/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H30" s="23" t="inlineStr">
@@ -30482,7 +30482,7 @@
           <t>G | 348呎 (2房)
 $691万
 $19,866/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="I30" s="23" t="inlineStr">
@@ -30490,7 +30490,7 @@
           <t>H | 348呎 (2房)
 $712万
 $20,455/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J30" s="23" t="inlineStr">
@@ -30498,7 +30498,7 @@
           <t>J | 464呎 (3房)
 $964万
 $20,777/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K30" s="23" t="inlineStr">
@@ -30506,7 +30506,7 @@
           <t>K | 395呎 (3房)
 $816万
 $20,661/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L30" s="23" t="inlineStr">
@@ -30514,7 +30514,7 @@
           <t>L | 270呎 (1房)
 $506万
 $18,743/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M30" s="23" t="inlineStr">
@@ -30522,7 +30522,7 @@
           <t>M | 265呎 (1房)
 $504万
 $19,015/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N30" s="21" t="inlineStr">
@@ -30538,7 +30538,7 @@
           <t>P | 273呎 (1房)
 $521万
 $19,091/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P30" s="23" t="inlineStr">
@@ -30546,7 +30546,7 @@
           <t>Q | 273呎 (1房)
 $516万
 $18,884/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -30561,7 +30561,7 @@
           <t>A | 512呎 (3房)
 $1025万
 $20,017/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -30569,7 +30569,7 @@
           <t>B | 397呎 (3房)
 $790万
 $19,909/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
@@ -30577,7 +30577,7 @@
           <t>C | 350呎 (2房)
 $702万
 $20,056/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
@@ -30585,7 +30585,7 @@
           <t>D | 350呎 (2房)
 $704万
 $20,110/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
@@ -30593,7 +30593,7 @@
           <t>E | 348呎 (2房)
 $701万
 $20,147/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G31" s="23" t="inlineStr">
@@ -30601,7 +30601,7 @@
           <t>F | 348呎 (2房)
 $703万
 $20,198/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H31" s="23" t="inlineStr">
@@ -30609,7 +30609,7 @@
           <t>G | 348呎 (2房)
 $701万
 $20,130/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="I31" s="23" t="inlineStr">
@@ -30617,7 +30617,7 @@
           <t>H | 348呎 (2房)
 $702万
 $20,182/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="J31" s="23" t="inlineStr">
@@ -30625,7 +30625,7 @@
           <t>J | 464呎 (3房)
 $951万
 $20,503/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="K31" s="23" t="inlineStr">
@@ -30633,7 +30633,7 @@
           <t>K | 395呎 (3房)
 $796万
 $20,152/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="L31" s="23" t="inlineStr">
@@ -30641,7 +30641,7 @@
           <t>L | 270呎 (1房)
 $532万
 $19,721/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M31" s="23" t="inlineStr">
@@ -30649,7 +30649,7 @@
           <t>M | 265呎 (1房)
 $531万
 $20,029/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="N31" s="23" t="inlineStr">
@@ -30657,7 +30657,7 @@
           <t>N | 349呎 (2房)
 $710万
 $20,358/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="O31" s="23" t="inlineStr">
@@ -30665,7 +30665,7 @@
           <t>P | 273呎 (1房)
 $548万
 $20,089/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="P31" s="23" t="inlineStr">
@@ -30673,7 +30673,7 @@
           <t>Q | 273呎 (1房)
 $542万
 $19,870/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-马头角-壹沐第2期.xlsx
+++ b/files/九龙-马头角-壹沐第2期.xlsx
@@ -27402,7 +27402,7 @@
           <t>C | 350呎 (2房)
 $911万
 $26,030/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -27410,7 +27410,7 @@
           <t>D | 350呎 (2房)
 $913万
 $26,084/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
@@ -27418,7 +27418,7 @@
           <t>E | 348呎 (2房)
 $862万
 $24,778/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="G6" s="23" t="inlineStr">
@@ -27426,7 +27426,7 @@
           <t>F | 348呎 (2房)
 $901万
 $25,893/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
@@ -27434,7 +27434,7 @@
           <t>G | 348呎 (2房)
 $853万
 $24,517/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr">
@@ -27442,7 +27442,7 @@
           <t>H | 348呎 (2房)
 $810万
 $23,276/呎
-(26年-05月)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
@@ -27466,7 +27466,7 @@
           <t>L | 270呎 (1房)
 $548万
 $20,300/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="M6" s="23" t="inlineStr">
@@ -27474,7 +27474,7 @@
           <t>M | 265呎 (1房)
 $546万
 $20,605/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="N6" s="21" t="inlineStr">
@@ -27490,7 +27490,7 @@
           <t>P | 273呎 (1房)
 $567万
 $20,763/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="P6" s="23" t="inlineStr">
@@ -27498,7 +27498,7 @@
           <t>Q | 273呎 (1房)
 $561万
 $20,565/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
     </row>
@@ -27513,7 +27513,7 @@
           <t>A | 512呎 (3房)
 $1196万
 $23,368/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -27521,7 +27521,7 @@
           <t>B | 397呎 (3房)
 $906万
 $22,831/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -27529,7 +27529,7 @@
           <t>C | 350呎 (2房)
 $803万
 $22,929/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
@@ -27537,7 +27537,7 @@
           <t>D | 350呎 (2房)
 $804万
 $22,978/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
@@ -27545,7 +27545,7 @@
           <t>E | 348呎 (2房)
 $802万
 $23,038/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -27593,7 +27593,7 @@
           <t>L | 270呎 (1房)
 $525万
 $19,430/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="M7" s="23" t="inlineStr">
@@ -27601,7 +27601,7 @@
           <t>M | 265呎 (1房)
 $552万
 $20,814/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="N7" s="21" t="inlineStr">
@@ -27617,7 +27617,7 @@
           <t>P | 273呎 (1房)
 $542万
 $19,840/呎
-(26年-05月)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="P7" s="23" t="inlineStr">
@@ -27625,7 +27625,7 @@
           <t>Q | 273呎 (1房)
 $536万
 $19,642/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
     </row>
@@ -27640,7 +27640,7 @@
           <t>A | 512呎 (3房)
 $1190万
 $23,237/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -27648,7 +27648,7 @@
           <t>B | 397呎 (3房)
 $901万
 $22,702/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -27656,7 +27656,7 @@
           <t>C | 350呎 (2房)
 $811万
 $23,181/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
@@ -27664,7 +27664,7 @@
           <t>D | 350呎 (2房)
 $844万
 $24,119/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -27672,7 +27672,7 @@
           <t>E | 348呎 (2房)
 $797万
 $22,909/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="G8" s="23" t="inlineStr">
@@ -27680,7 +27680,7 @@
           <t>F | 348呎 (2房)
 $858万
 $24,644/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -27720,7 +27720,7 @@
           <t>L | 270呎 (1房)
 $523万
 $19,373/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="M8" s="23" t="inlineStr">
@@ -27728,7 +27728,7 @@
           <t>M | 265呎 (1房)
 $521万
 $19,661/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="N8" s="21" t="inlineStr">
@@ -27744,7 +27744,7 @@
           <t>P | 273呎 (1房)
 $543万
 $19,893/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="P8" s="23" t="inlineStr">
@@ -27752,7 +27752,7 @@
           <t>Q | 273呎 (1房)
 $535万
 $19,586/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -27767,7 +27767,7 @@
           <t>A | 512呎 (3房)
 $1218万
 $23,783/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -27775,7 +27775,7 @@
           <t>B | 397呎 (3房)
 $946万
 $23,829/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -27783,7 +27783,7 @@
           <t>C | 350呎 (2房)
 $794万
 $22,672/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -27791,7 +27791,7 @@
           <t>D | 350呎 (2房)
 $795万
 $22,724/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
@@ -27799,7 +27799,7 @@
           <t>E | 348呎 (2房)
 $837万
 $24,045/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -27847,7 +27847,7 @@
           <t>L | 270呎 (1房)
 $522万
 $19,320/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="M9" s="23" t="inlineStr">
@@ -27855,7 +27855,7 @@
           <t>M | 265呎 (1房)
 $520万
 $19,606/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="N9" s="21" t="inlineStr">
@@ -27871,7 +27871,7 @@
           <t>P | 273呎 (1房)
 $538万
 $19,724/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="P9" s="23" t="inlineStr">
@@ -27879,7 +27879,7 @@
           <t>Q | 273呎 (1房)
 $533万
 $19,526/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
           <t>A | 512呎 (3房)
 $1211万
 $23,648/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -27902,7 +27902,7 @@
           <t>B | 397呎 (3房)
 $954万
 $24,029/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -27910,7 +27910,7 @@
           <t>C | 350呎 (2房)
 $833万
 $23,796/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -27918,7 +27918,7 @@
           <t>D | 350呎 (2房)
 $835万
 $23,850/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -27926,7 +27926,7 @@
           <t>E | 348呎 (2房)
 $788万
 $22,650/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -27942,7 +27942,7 @@
           <t>G | 348呎 (2房)
 $761万
 $21,861/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="I10" s="23" t="inlineStr">
@@ -27950,7 +27950,7 @@
           <t>H | 348呎 (2房)
 $805万
 $23,128/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -27974,7 +27974,7 @@
           <t>L | 270呎 (1房)
 $523万
 $19,374/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="M10" s="23" t="inlineStr">
@@ -27982,7 +27982,7 @@
           <t>M | 265呎 (1房)
 $547万
 $20,638/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="N10" s="21" t="inlineStr">
@@ -27998,7 +27998,7 @@
           <t>P | 273呎 (1房)
 $537万
 $19,668/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="P10" s="23" t="inlineStr">
@@ -28006,7 +28006,7 @@
           <t>Q | 273呎 (1房)
 $534万
 $19,578/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -28021,7 +28021,7 @@
           <t>A | 512呎 (3房)
 $1161万
 $22,671/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -28037,7 +28037,7 @@
           <t>C | 350呎 (2房)
 $812万
 $23,207/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -28045,7 +28045,7 @@
           <t>D | 350呎 (2房)
 $828万
 $23,646/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
@@ -28053,7 +28053,7 @@
           <t>E | 348呎 (2房)
 $816万
 $23,444/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -28069,7 +28069,7 @@
           <t>G | 348呎 (2房)
 $761万
 $21,861/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="I11" s="23" t="inlineStr">
@@ -28077,7 +28077,7 @@
           <t>H | 348呎 (2房)
 $813万
 $23,371/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="J11" s="23" t="inlineStr">
@@ -28085,7 +28085,7 @@
           <t>J | 464呎 (3房)
 $1133万
 $24,417/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
@@ -28101,7 +28101,7 @@
           <t>L | 270呎 (1房)
 $523万
 $19,374/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="M11" s="23" t="inlineStr">
@@ -28109,7 +28109,7 @@
           <t>M | 265呎 (1房)
 $518万
 $19,552/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="N11" s="21" t="inlineStr">
@@ -28133,7 +28133,7 @@
           <t>Q | 273呎 (1房)
 $601万
 $22,002/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
     </row>
@@ -28148,7 +28148,7 @@
           <t>A | 512呎 (3房)
 $1148万
 $22,412/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -28156,7 +28156,7 @@
           <t>B | 397呎 (3房)
 $933万
 $23,491/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -28164,7 +28164,7 @@
           <t>C | 350呎 (2房)
 $807万
 $23,070/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -28172,7 +28172,7 @@
           <t>D | 350呎 (2房)
 $805万
 $22,994/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
@@ -28180,7 +28180,7 @@
           <t>E | 348呎 (2房)
 $802万
 $23,051/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -28196,7 +28196,7 @@
           <t>G | 348呎 (2房)
 $752万
 $21,613/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="I12" s="23" t="inlineStr">
@@ -28204,7 +28204,7 @@
           <t>H | 348呎 (2房)
 $804万
 $23,106/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="J12" s="23" t="inlineStr">
@@ -28212,7 +28212,7 @@
           <t>J | 464呎 (3房)
 $1061万
 $22,872/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr">
@@ -28228,7 +28228,7 @@
           <t>L | 270呎 (1房)
 $517万
 $19,157/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="M12" s="23" t="inlineStr">
@@ -28236,7 +28236,7 @@
           <t>M | 265呎 (1房)
 $544万
 $20,520/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="N12" s="21" t="inlineStr">
@@ -28260,7 +28260,7 @@
           <t>Q | 273呎 (1房)
 $597万
 $21,870/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
     </row>
@@ -28275,7 +28275,7 @@
           <t>A | 512呎 (3房)
 $1141万
 $22,282/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -28283,7 +28283,7 @@
           <t>B | 397呎 (3房)
 $927万
 $23,355/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -28291,7 +28291,7 @@
           <t>C | 350呎 (2房)
 $798万
 $22,811/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -28299,7 +28299,7 @@
           <t>D | 350呎 (2房)
 $800万
 $22,860/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="F13" s="23" t="inlineStr">
@@ -28307,7 +28307,7 @@
           <t>E | 348呎 (2房)
 $797万
 $22,916/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -28323,7 +28323,7 @@
           <t>G | 348呎 (2房)
 $824万
 $23,677/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="I13" s="23" t="inlineStr">
@@ -28331,7 +28331,7 @@
           <t>H | 348呎 (2房)
 $799万
 $22,974/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="J13" s="23" t="inlineStr">
@@ -28339,7 +28339,7 @@
           <t>J | 464呎 (3房)
 $1055万
 $22,742/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -28355,7 +28355,7 @@
           <t>L | 270呎 (1房)
 $583万
 $21,583/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="M13" s="23" t="inlineStr">
@@ -28363,7 +28363,7 @@
           <t>M | 265呎 (1房)
 $580万
 $21,906/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="N13" s="21" t="inlineStr">
@@ -28387,7 +28387,7 @@
           <t>Q | 273呎 (1房)
 $595万
 $21,808/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
     </row>
@@ -28402,7 +28402,7 @@
           <t>A | 512呎 (3房)
 $1134万
 $22,152/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -28410,7 +28410,7 @@
           <t>B | 397呎 (3房)
 $973万
 $24,509/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -28418,7 +28418,7 @@
           <t>C | 350呎 (2房)
 $794万
 $22,677/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
@@ -28426,7 +28426,7 @@
           <t>D | 350呎 (2房)
 $796万
 $22,729/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="F14" s="23" t="inlineStr">
@@ -28434,7 +28434,7 @@
           <t>E | 348呎 (2房)
 $797万
 $22,911/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -28450,7 +28450,7 @@
           <t>G | 348呎 (2房)
 $819万
 $23,540/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="I14" s="23" t="inlineStr">
@@ -28458,7 +28458,7 @@
           <t>H | 348呎 (2房)
 $821万
 $23,594/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="J14" s="23" t="inlineStr">
@@ -28466,7 +28466,7 @@
           <t>J | 464呎 (3房)
 $1107万
 $23,867/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -28482,7 +28482,7 @@
           <t>L | 270呎 (1房)
 $581万
 $21,523/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="M14" s="23" t="inlineStr">
@@ -28490,7 +28490,7 @@
           <t>M | 265呎 (1房)
 $579万
 $21,841/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="N14" s="21" t="inlineStr">
@@ -28514,7 +28514,7 @@
           <t>Q | 273呎 (1房)
 $594万
 $21,742/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -28529,7 +28529,7 @@
           <t>A | 512呎 (3房)
 $1126万
 $21,987/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -28537,7 +28537,7 @@
           <t>B | 397呎 (3房)
 $891万
 $22,443/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -28545,7 +28545,7 @@
           <t>C | 350呎 (2房)
 $789万
 $22,546/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -28553,7 +28553,7 @@
           <t>D | 350呎 (2房)
 $835万
 $23,853/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
@@ -28561,7 +28561,7 @@
           <t>E | 348呎 (2房)
 $788万
 $22,650/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="G15" s="23" t="inlineStr">
@@ -28569,7 +28569,7 @@
           <t>F | 348呎 (2房)
 $824万
 $23,674/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="H15" s="23" t="inlineStr">
@@ -28577,7 +28577,7 @@
           <t>G | 348呎 (2房)
 $814万
 $23,403/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -28593,7 +28593,7 @@
           <t>J | 464呎 (3房)
 $1043万
 $22,481/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -28609,7 +28609,7 @@
           <t>L | 270呎 (1房)
 $580万
 $21,463/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="M15" s="23" t="inlineStr">
@@ -28617,7 +28617,7 @@
           <t>M | 265呎 (1房)
 $577万
 $21,780/呎
-(26年-05月)</t>
+(26年-05月-30日)</t>
         </is>
       </c>
       <c r="N15" s="21" t="inlineStr">
@@ -28633,7 +28633,7 @@
           <t>P | 273呎 (1房)
 $529万
 $19,381/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="P15" s="23" t="inlineStr">
@@ -28641,7 +28641,7 @@
           <t>Q | 273呎 (1房)
 $524万
 $19,184/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
     </row>
@@ -28656,7 +28656,7 @@
           <t>A | 512呎 (3房)
 $1136万
 $22,184/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -28664,7 +28664,7 @@
           <t>B | 397呎 (3房)
 $860万
 $21,675/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -28672,7 +28672,7 @@
           <t>C | 350呎 (2房)
 $793万
 $22,645/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -28680,7 +28680,7 @@
           <t>D | 350呎 (2房)
 $794万
 $22,697/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
@@ -28688,7 +28688,7 @@
           <t>E | 348呎 (2房)
 $792万
 $22,751/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -28704,7 +28704,7 @@
           <t>G | 348呎 (2房)
 $810万
 $23,266/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="I16" s="23" t="inlineStr">
@@ -28712,7 +28712,7 @@
           <t>H | 348呎 (2房)
 $812万
 $23,320/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="J16" s="23" t="inlineStr">
@@ -28720,7 +28720,7 @@
           <t>J | 464呎 (3房)
 $1084万
 $23,352/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr">
@@ -28728,7 +28728,7 @@
           <t>K | 395呎 (3房)
 $845万
 $21,384/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="L16" s="23" t="inlineStr">
@@ -28736,7 +28736,7 @@
           <t>L | 270呎 (1房)
 $511万
 $18,937/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="M16" s="23" t="inlineStr">
@@ -28744,7 +28744,7 @@
           <t>M | 265呎 (1房)
 $575万
 $21,715/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="N16" s="21" t="inlineStr">
@@ -28760,7 +28760,7 @@
           <t>P | 273呎 (1房)
 $527万
 $19,322/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="P16" s="23" t="inlineStr">
@@ -28768,7 +28768,7 @@
           <t>Q | 273呎 (1房)
 $522万
 $19,124/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -28783,7 +28783,7 @@
           <t>A | 512呎 (3房)
 $1129万
 $22,052/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -28791,7 +28791,7 @@
           <t>B | 397呎 (3房)
 $855万
 $21,546/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -28799,7 +28799,7 @@
           <t>C | 350呎 (2房)
 $746万
 $21,327/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -28807,7 +28807,7 @@
           <t>D | 350呎 (2房)
 $790万
 $22,564/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
@@ -28815,7 +28815,7 @@
           <t>E | 348呎 (2房)
 $746万
 $21,427/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="G17" s="23" t="inlineStr">
@@ -28823,7 +28823,7 @@
           <t>F | 348呎 (2房)
 $814万
 $23,397/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="H17" s="23" t="inlineStr">
@@ -28831,7 +28831,7 @@
           <t>G | 348呎 (2房)
 $850万
 $24,416/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="I17" s="23" t="inlineStr">
@@ -28839,7 +28839,7 @@
           <t>H | 348呎 (2房)
 $807万
 $23,183/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="J17" s="23" t="inlineStr">
@@ -28847,7 +28847,7 @@
           <t>J | 464呎 (3房)
 $1077万
 $23,214/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="K17" s="23" t="inlineStr">
@@ -28855,7 +28855,7 @@
           <t>K | 395呎 (3房)
 $882万
 $22,332/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="L17" s="23" t="inlineStr">
@@ -28863,7 +28863,7 @@
           <t>L | 270呎 (1房)
 $538万
 $19,932/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="M17" s="23" t="inlineStr">
@@ -28871,7 +28871,7 @@
           <t>M | 265呎 (1房)
 $508万
 $19,162/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="N17" s="21" t="inlineStr">
@@ -28887,7 +28887,7 @@
           <t>P | 273呎 (1房)
 $555万
 $20,336/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="P17" s="23" t="inlineStr">
@@ -28895,7 +28895,7 @@
           <t>Q | 273呎 (1房)
 $521万
 $19,068/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -28910,7 +28910,7 @@
           <t>A | 512呎 (3房)
 $1256万
 $24,537/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -28918,7 +28918,7 @@
           <t>B | 397呎 (3房)
 $850万
 $21,416/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -28926,7 +28926,7 @@
           <t>C | 350呎 (2房)
 $783万
 $22,379/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -28934,7 +28934,7 @@
           <t>D | 350呎 (2房)
 $744万
 $21,250/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
@@ -28942,7 +28942,7 @@
           <t>E | 348呎 (2房)
 $741万
 $21,300/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -28958,7 +28958,7 @@
           <t>G | 348呎 (2房)
 $800万
 $22,994/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="I18" s="23" t="inlineStr">
@@ -28966,7 +28966,7 @@
           <t>H | 348呎 (2房)
 $847万
 $24,326/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -28982,7 +28982,7 @@
           <t>K | 395呎 (3房)
 $872万
 $22,074/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="L18" s="23" t="inlineStr">
@@ -28990,7 +28990,7 @@
           <t>L | 270呎 (1房)
 $509万
 $18,863/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="M18" s="23" t="inlineStr">
@@ -28998,7 +28998,7 @@
           <t>M | 265呎 (1房)
 $534万
 $20,169/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="N18" s="21" t="inlineStr">
@@ -29014,7 +29014,7 @@
           <t>P | 273呎 (1房)
 $553万
 $20,274/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="P18" s="23" t="inlineStr">
@@ -29022,7 +29022,7 @@
           <t>Q | 273呎 (1房)
 $519万
 $19,009/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
     </row>
@@ -29037,7 +29037,7 @@
           <t>A | 512呎 (3房)
 $1183万
 $23,105/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -29045,7 +29045,7 @@
           <t>B | 397呎 (3房)
 $845万
 $21,287/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -29053,7 +29053,7 @@
           <t>C | 350呎 (2房)
 $738万
 $21,075/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -29061,7 +29061,7 @@
           <t>D | 350呎 (2房)
 $739万
 $21,124/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
@@ -29069,7 +29069,7 @@
           <t>E | 348呎 (2房)
 $737万
 $21,173/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -29085,7 +29085,7 @@
           <t>G | 348呎 (2房)
 $795万
 $22,857/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="I19" s="23" t="inlineStr">
@@ -29093,7 +29093,7 @@
           <t>H | 348呎 (2房)
 $797万
 $22,909/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -29109,7 +29109,7 @@
           <t>K | 395呎 (3房)
 $867万
 $21,942/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="L19" s="23" t="inlineStr">
@@ -29117,7 +29117,7 @@
           <t>L | 270呎 (1房)
 $536万
 $19,866/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="M19" s="23" t="inlineStr">
@@ -29125,7 +29125,7 @@
           <t>M | 265呎 (1房)
 $503万
 $18,995/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="N19" s="21" t="inlineStr">
@@ -29141,7 +29141,7 @@
           <t>P | 273呎 (1房)
 $521万
 $19,095/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="P19" s="23" t="inlineStr">
@@ -29149,7 +29149,7 @@
           <t>Q | 273呎 (1房)
 $545万
 $19,947/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -29172,7 +29172,7 @@
           <t>B | 397呎 (3房)
 $870万
 $21,906/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -29212,7 +29212,7 @@
           <t>G | 348呎 (2房)
 $795万
 $22,857/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="I20" s="23" t="inlineStr">
@@ -29220,7 +29220,7 @@
           <t>H | 348呎 (2房)
 $797万
 $22,909/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
@@ -29236,7 +29236,7 @@
           <t>K | 395呎 (3房)
 $876万
 $22,186/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="L20" s="23" t="inlineStr">
@@ -29244,7 +29244,7 @@
           <t>L | 270呎 (1房)
 $508万
 $18,800/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="M20" s="23" t="inlineStr">
@@ -29252,7 +29252,7 @@
           <t>M | 265呎 (1房)
 $503万
 $18,995/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="N20" s="21" t="inlineStr">
@@ -29268,7 +29268,7 @@
           <t>P | 273呎 (1房)
 $521万
 $19,095/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="P20" s="23" t="inlineStr">
@@ -29276,7 +29276,7 @@
           <t>Q | 273呎 (1房)
 $516万
 $18,897/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -29291,7 +29291,7 @@
           <t>A | 512呎 (3房)
 $1251万
 $24,437/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -29299,7 +29299,7 @@
           <t>B | 397呎 (3房)
 $896万
 $22,575/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -29307,7 +29307,7 @@
           <t>C | 350呎 (2房)
 $794万
 $22,695/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -29315,7 +29315,7 @@
           <t>D | 350呎 (2房)
 $796万
 $22,747/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
@@ -29323,7 +29323,7 @@
           <t>E | 348呎 (2房)
 $793万
 $22,800/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -29339,7 +29339,7 @@
           <t>G | 348呎 (2房)
 $786万
 $22,583/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="I21" s="23" t="inlineStr">
@@ -29347,7 +29347,7 @@
           <t>H | 348呎 (2房)
 $788万
 $22,637/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -29363,7 +29363,7 @@
           <t>K | 395呎 (3房)
 $856万
 $21,675/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="L21" s="23" t="inlineStr">
@@ -29371,7 +29371,7 @@
           <t>L | 270呎 (1房)
 $568万
 $21,044/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="M21" s="23" t="inlineStr">
@@ -29379,7 +29379,7 @@
           <t>M | 265呎 (1房)
 $501万
 $18,917/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="N21" s="21" t="inlineStr">
@@ -29395,7 +29395,7 @@
           <t>P | 273呎 (1房)
 $518万
 $18,979/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="P21" s="23" t="inlineStr">
@@ -29403,7 +29403,7 @@
           <t>Q | 273呎 (1房)
 $514万
 $18,814/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -29466,7 +29466,7 @@
           <t>G | 348呎 (2房)
 $794万
 $22,820/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
@@ -29474,7 +29474,7 @@
           <t>H | 348呎 (2房)
 $792万
 $22,750/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -29490,7 +29490,7 @@
           <t>K | 395呎 (3房)
 $924万
 $23,387/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="L22" s="23" t="inlineStr">
@@ -29498,7 +29498,7 @@
           <t>L | 270呎 (1房)
 $537万
 $19,877/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="M22" s="23" t="inlineStr">
@@ -29506,7 +29506,7 @@
           <t>M | 265呎 (1房)
 $535万
 $20,170/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="N22" s="21" t="inlineStr">
@@ -29522,7 +29522,7 @@
           <t>P | 273呎 (1房)
 $553万
 $20,268/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="P22" s="23" t="inlineStr">
@@ -29530,7 +29530,7 @@
           <t>Q | 273呎 (1房)
 $548万
 $20,057/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -29593,7 +29593,7 @@
           <t>G | 348呎 (2房)
 $767万
 $22,037/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="I23" s="23" t="inlineStr">
@@ -29601,7 +29601,7 @@
           <t>H | 348呎 (2房)
 $769万
 $22,089/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -29617,7 +29617,7 @@
           <t>K | 395呎 (3房)
 $809万
 $20,493/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="L23" s="23" t="inlineStr">
@@ -29625,7 +29625,7 @@
           <t>L | 270呎 (1房)
 $562万
 $20,798/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="M23" s="23" t="inlineStr">
@@ -29633,7 +29633,7 @@
           <t>M | 265呎 (1房)
 $530万
 $19,990/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="N23" s="21" t="inlineStr">
@@ -29649,7 +29649,7 @@
           <t>P | 273呎 (1房)
 $579万
 $21,199/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="P23" s="23" t="inlineStr">
@@ -29657,7 +29657,7 @@
           <t>Q | 273呎 (1房)
 $573万
 $20,973/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -29680,7 +29680,7 @@
           <t>B | 397呎 (3房)
 $850万
 $21,401/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -29688,7 +29688,7 @@
           <t>C | 350呎 (2房)
 $691万
 $19,746/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
@@ -29696,7 +29696,7 @@
           <t>D | 350呎 (2房)
 $693万
 $19,795/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="F24" s="23" t="inlineStr">
@@ -29704,7 +29704,7 @@
           <t>E | 348呎 (2房)
 $690万
 $19,836/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -29720,7 +29720,7 @@
           <t>G | 348呎 (2房)
 $745万
 $21,422/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="I24" s="23" t="inlineStr">
@@ -29728,7 +29728,7 @@
           <t>H | 348呎 (2房)
 $760万
 $21,831/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -29744,7 +29744,7 @@
           <t>K | 395呎 (3房)
 $804万
 $20,365/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="L24" s="23" t="inlineStr">
@@ -29752,7 +29752,7 @@
           <t>L | 270呎 (1房)
 $566万
 $20,953/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="M24" s="23" t="inlineStr">
@@ -29760,7 +29760,7 @@
           <t>M | 265呎 (1房)
 $528万
 $19,932/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="N24" s="21" t="inlineStr">
@@ -29776,7 +29776,7 @@
           <t>P | 273呎 (1房)
 $547万
 $20,021/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="P24" s="23" t="inlineStr">
@@ -29784,7 +29784,7 @@
           <t>Q | 273呎 (1房)
 $541万
 $19,810/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -29815,7 +29815,7 @@
           <t>C | 350呎 (2房)
 $684万
 $19,556/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
@@ -29823,7 +29823,7 @@
           <t>D | 350呎 (2房)
 $686万
 $19,605/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
@@ -29831,7 +29831,7 @@
           <t>E | 348呎 (2房)
 $684万
 $19,645/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="G25" s="23" t="inlineStr">
@@ -29839,7 +29839,7 @@
           <t>F | 348呎 (2房)
 $788万
 $22,650/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -29871,7 +29871,7 @@
           <t>K | 395呎 (3房)
 $794万
 $20,110/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="L25" s="23" t="inlineStr">
@@ -29879,7 +29879,7 @@
           <t>L | 270呎 (1房)
 $529万
 $19,587/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="M25" s="23" t="inlineStr">
@@ -29887,7 +29887,7 @@
           <t>M | 265呎 (1房)
 $527万
 $19,871/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="N25" s="21" t="inlineStr">
@@ -29903,7 +29903,7 @@
           <t>P | 273呎 (1房)
 $575万
 $21,067/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="P25" s="23" t="inlineStr">
@@ -29911,7 +29911,7 @@
           <t>Q | 273呎 (1房)
 $539万
 $19,747/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -29942,7 +29942,7 @@
           <t>C | 350呎 (2房)
 $680万
 $19,430/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="E26" s="23" t="inlineStr">
@@ -29950,7 +29950,7 @@
           <t>D | 350呎 (2房)
 $682万
 $19,479/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="F26" s="23" t="inlineStr">
@@ -29958,7 +29958,7 @@
           <t>E | 348呎 (2房)
 $679万
 $19,518/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -29998,7 +29998,7 @@
           <t>K | 395呎 (3房)
 $779万
 $19,729/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="L26" s="23" t="inlineStr">
@@ -30006,7 +30006,7 @@
           <t>L | 270呎 (1房)
 $555万
 $20,566/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="M26" s="23" t="inlineStr">
@@ -30014,7 +30014,7 @@
           <t>M | 265呎 (1房)
 $553万
 $20,864/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="N26" s="21" t="inlineStr">
@@ -30030,7 +30030,7 @@
           <t>P | 273呎 (1房)
 $543万
 $19,899/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="P26" s="23" t="inlineStr">
@@ -30038,7 +30038,7 @@
           <t>Q | 273呎 (1房)
 $537万
 $19,685/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -30053,7 +30053,7 @@
           <t>A | 512呎 (3房)
 $1081万
 $21,117/呎
-(26年-07月)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -30069,7 +30069,7 @@
           <t>C | 350呎 (2房)
 $713万
 $20,376/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="E27" s="23" t="inlineStr">
@@ -30077,7 +30077,7 @@
           <t>D | 350呎 (2房)
 $677万
 $19,353/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
@@ -30085,7 +30085,7 @@
           <t>E | 348呎 (2房)
 $712万
 $20,469/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -30101,7 +30101,7 @@
           <t>G | 348呎 (2房)
 $739万
 $21,233/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="I27" s="23" t="inlineStr">
@@ -30109,7 +30109,7 @@
           <t>H | 348呎 (2房)
 $741万
 $21,287/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
@@ -30125,7 +30125,7 @@
           <t>K | 395呎 (3房)
 $785万
 $19,864/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="L27" s="23" t="inlineStr">
@@ -30133,7 +30133,7 @@
           <t>L | 270呎 (1房)
 $548万
 $20,303/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="M27" s="23" t="inlineStr">
@@ -30141,7 +30141,7 @@
           <t>M | 265呎 (1房)
 $546万
 $20,598/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="N27" s="21" t="inlineStr">
@@ -30157,7 +30157,7 @@
           <t>P | 273呎 (1房)
 $588万
 $21,537/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="P27" s="23" t="inlineStr">
@@ -30165,7 +30165,7 @@
           <t>Q | 273呎 (1房)
 $551万
 $20,186/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
     </row>
@@ -30196,7 +30196,7 @@
           <t>C | 350呎 (2房)
 $676万
 $19,304/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="E28" s="23" t="inlineStr">
@@ -30204,7 +30204,7 @@
           <t>D | 350呎 (2房)
 $677万
 $19,353/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="F28" s="23" t="inlineStr">
@@ -30212,7 +30212,7 @@
           <t>E | 348呎 (2房)
 $675万
 $19,391/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
@@ -30220,7 +30220,7 @@
           <t>F | 348呎 (2房)
 $737万
 $21,178/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="H28" s="23" t="inlineStr">
@@ -30228,7 +30228,7 @@
           <t>G | 348呎 (2房)
 $739万
 $21,233/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="I28" s="23" t="inlineStr">
@@ -30236,7 +30236,7 @@
           <t>H | 348呎 (2房)
 $749万
 $21,524/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">
@@ -30252,7 +30252,7 @@
           <t>K | 395呎 (3房)
 $772万
 $19,538/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="L28" s="23" t="inlineStr">
@@ -30260,7 +30260,7 @@
           <t>L | 270呎 (1房)
 $548万
 $20,303/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="M28" s="23" t="inlineStr">
@@ -30268,7 +30268,7 @@
           <t>M | 265呎 (1房)
 $546万
 $20,598/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="N28" s="21" t="inlineStr">
@@ -30284,7 +30284,7 @@
           <t>P | 273呎 (1房)
 $557万
 $20,403/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="P28" s="23" t="inlineStr">
@@ -30292,7 +30292,7 @@
           <t>Q | 273呎 (1房)
 $554万
 $20,298/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -30307,7 +30307,7 @@
           <t>A | 512呎 (3房)
 $993万
 $19,392/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
@@ -30323,7 +30323,7 @@
           <t>C | 350呎 (2房)
 $716万
 $20,471/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="E29" s="23" t="inlineStr">
@@ -30331,7 +30331,7 @@
           <t>D | 350呎 (2房)
 $718万
 $20,523/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
@@ -30339,7 +30339,7 @@
           <t>E | 348呎 (2房)
 $716万
 $20,563/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
@@ -30347,7 +30347,7 @@
           <t>F | 348呎 (2房)
 $727万
 $20,902/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="H29" s="23" t="inlineStr">
@@ -30355,7 +30355,7 @@
           <t>G | 348呎 (2房)
 $729万
 $20,956/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="I29" s="23" t="inlineStr">
@@ -30363,7 +30363,7 @@
           <t>H | 348呎 (2房)
 $731万
 $21,010/呎
-(26年-06月)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="J29" s="23" t="inlineStr">
@@ -30371,7 +30371,7 @@
           <t>J | 464呎 (3房)
 $928万
 $19,990/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="K29" s="23" t="inlineStr">
@@ -30379,7 +30379,7 @@
           <t>K | 395呎 (3房)
 $761万
 $19,262/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="L29" s="23" t="inlineStr">
@@ -30387,7 +30387,7 @@
           <t>L | 270呎 (1房)
 $545万
 $20,180/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="M29" s="23" t="inlineStr">
@@ -30395,7 +30395,7 @@
           <t>M | 265呎 (1房)
 $543万
 $20,486/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
       <c r="N29" s="21" t="inlineStr">
@@ -30411,7 +30411,7 @@
           <t>P | 273呎 (1房)
 $554万
 $20,275/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="P29" s="23" t="inlineStr">
@@ -30419,7 +30419,7 @@
           <t>Q | 273呎 (1房)
 $579万
 $21,220/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -30434,7 +30434,7 @@
           <t>A | 512呎 (3房)
 $983万
 $19,199/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -30442,7 +30442,7 @@
           <t>B | 397呎 (3房)
 $811万
 $20,435/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
@@ -30450,7 +30450,7 @@
           <t>C | 350呎 (2房)
 $713万
 $20,378/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
@@ -30458,7 +30458,7 @@
           <t>D | 350呎 (2房)
 $751万
 $21,448/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="F30" s="23" t="inlineStr">
@@ -30466,7 +30466,7 @@
           <t>E | 348呎 (2房)
 $708万
 $20,359/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="G30" s="23" t="inlineStr">
@@ -30474,7 +30474,7 @@
           <t>F | 348呎 (2房)
 $760万
 $21,845/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="H30" s="23" t="inlineStr">
@@ -30482,7 +30482,7 @@
           <t>G | 348呎 (2房)
 $691万
 $19,866/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="I30" s="23" t="inlineStr">
@@ -30490,7 +30490,7 @@
           <t>H | 348呎 (2房)
 $712万
 $20,455/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="J30" s="23" t="inlineStr">
@@ -30498,7 +30498,7 @@
           <t>J | 464呎 (3房)
 $964万
 $20,777/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="K30" s="23" t="inlineStr">
@@ -30506,7 +30506,7 @@
           <t>K | 395呎 (3房)
 $816万
 $20,661/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="L30" s="23" t="inlineStr">
@@ -30514,7 +30514,7 @@
           <t>L | 270呎 (1房)
 $506万
 $18,743/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="M30" s="23" t="inlineStr">
@@ -30522,7 +30522,7 @@
           <t>M | 265呎 (1房)
 $504万
 $19,015/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="N30" s="21" t="inlineStr">
@@ -30538,7 +30538,7 @@
           <t>P | 273呎 (1房)
 $521万
 $19,091/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="P30" s="23" t="inlineStr">
@@ -30546,7 +30546,7 @@
           <t>Q | 273呎 (1房)
 $516万
 $18,884/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -30561,7 +30561,7 @@
           <t>A | 512呎 (3房)
 $1025万
 $20,017/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -30569,7 +30569,7 @@
           <t>B | 397呎 (3房)
 $790万
 $19,909/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
@@ -30577,7 +30577,7 @@
           <t>C | 350呎 (2房)
 $702万
 $20,056/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
@@ -30585,7 +30585,7 @@
           <t>D | 350呎 (2房)
 $704万
 $20,110/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
@@ -30593,7 +30593,7 @@
           <t>E | 348呎 (2房)
 $701万
 $20,147/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="G31" s="23" t="inlineStr">
@@ -30601,7 +30601,7 @@
           <t>F | 348呎 (2房)
 $703万
 $20,198/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="H31" s="23" t="inlineStr">
@@ -30609,7 +30609,7 @@
           <t>G | 348呎 (2房)
 $701万
 $20,130/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="I31" s="23" t="inlineStr">
@@ -30617,7 +30617,7 @@
           <t>H | 348呎 (2房)
 $702万
 $20,182/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="J31" s="23" t="inlineStr">
@@ -30625,7 +30625,7 @@
           <t>J | 464呎 (3房)
 $951万
 $20,503/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="K31" s="23" t="inlineStr">
@@ -30633,7 +30633,7 @@
           <t>K | 395呎 (3房)
 $796万
 $20,152/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="L31" s="23" t="inlineStr">
@@ -30641,7 +30641,7 @@
           <t>L | 270呎 (1房)
 $532万
 $19,721/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="M31" s="23" t="inlineStr">
@@ -30649,7 +30649,7 @@
           <t>M | 265呎 (1房)
 $531万
 $20,029/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="N31" s="23" t="inlineStr">
@@ -30657,7 +30657,7 @@
           <t>N | 349呎 (2房)
 $710万
 $20,358/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="O31" s="23" t="inlineStr">
@@ -30665,7 +30665,7 @@
           <t>P | 273呎 (1房)
 $548万
 $20,089/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="P31" s="23" t="inlineStr">
@@ -30673,7 +30673,7 @@
           <t>Q | 273呎 (1房)
 $542万
 $19,870/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-马头角-壹沐第2期.xlsx
+++ b/files/九龙-马头角-壹沐第2期.xlsx
@@ -8693,23 +8693,23 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
-        <v>9261000</v>
+        <v>8334900</v>
       </c>
       <c r="I128" s="5" t="n">
-        <v>26612</v>
+        <v>23951</v>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K128" s="5" t="n">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="M128" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N128" s="3" t="inlineStr">
@@ -27170,7 +27170,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -27180,7 +27180,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>282</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -28310,12 +28310,12 @@
 (26年-05月-31日)</t>
         </is>
       </c>
-      <c r="G13" s="20" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>F | 348呎 (2房)
-$926万
-$26,612/呎
-(在售)</t>
+$833万
+$23,951/呎
+(26年-07月-19日)</t>
         </is>
       </c>
       <c r="H13" s="23" t="inlineStr">
